--- a/GearSage-client/rate/excel/hook.xlsx
+++ b/GearSage-client/rate/excel/hook.xlsx
@@ -32,11 +32,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
   </numFmts>
   <fonts count="1">
@@ -401,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K72"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1523,9 +1519,1409 @@
         <v>The Big Cat Circle hook is built for tough-lipped catfish with an offset, precision-sharpened point and an up eye for quick snelling. The page positions it as a heavy-duty forged circle hook for very large catfish.</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>OHK1000</v>
+      </c>
+      <c r="B33">
+        <v>46</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Jungle Drop Shot</v>
+      </c>
+      <c r="D33" t="str">
+        <v/>
+      </c>
+      <c r="E33" t="str">
+        <v/>
+      </c>
+      <c r="F33" t="str">
+        <v/>
+      </c>
+      <c r="G33" t="str">
+        <v>倒钓钩 / Drop Shot</v>
+      </c>
+      <c r="H33" t="str">
+        <v>pkgGear/images/hook/OWNER/jungle_drop_shot.gif</v>
+      </c>
+      <c r="I33" t="str">
+        <v/>
+      </c>
+      <c r="J33" t="str">
+        <v/>
+      </c>
+      <c r="K33" t="str">
+        <v>JUNGLE DROP SHOT Hooks feature an extended shank for powerful hook sets and keeps the knot out of the fish’s mouth and away from sharp teeth, reducing down-time from frequent re-tying. The beaked Super Needle Point offers superior penetration and fish holding ability. Try them nose hooked or thread them though your bait for a [&amp;hellip;]</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>OHK1001</v>
+      </c>
+      <c r="B34">
+        <v>46</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Multi-Offset</v>
+      </c>
+      <c r="D34" t="str">
+        <v/>
+      </c>
+      <c r="E34" t="str">
+        <v/>
+      </c>
+      <c r="F34" t="str">
+        <v/>
+      </c>
+      <c r="G34" t="str">
+        <v>曲柄钩 / Offset / Wide Gap</v>
+      </c>
+      <c r="H34" t="str">
+        <v>pkgGear/images/hook/OWNER/multi_offset.gif</v>
+      </c>
+      <c r="I34" t="str">
+        <v/>
+      </c>
+      <c r="J34" t="str">
+        <v/>
+      </c>
+      <c r="K34" t="str">
+        <v>World-renowned designer Haruhiko Murakami (creator of the Drop-Shot and Neko-Rig techniques) partnered with Owner Japan to help create the revolutionary Multi-Offset Hook. The Multi-Offset Hook offers efficiency and versatility like no other. The vertically oriented Straight Eye keeps the knot in-line; offering more linear bait retrieval and more powerful hooksets. The enlarged eye also allows [&amp;hellip;]</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>OHK1002</v>
+      </c>
+      <c r="B35">
+        <v>46</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Ringed All Purpose Softbait Hook</v>
+      </c>
+      <c r="D35" t="str">
+        <v/>
+      </c>
+      <c r="E35" t="str">
+        <v/>
+      </c>
+      <c r="F35" t="str">
+        <v/>
+      </c>
+      <c r="G35" t="str">
+        <v>特种钩 / Bass Hook</v>
+      </c>
+      <c r="H35" t="str">
+        <v>pkgGear/images/hook/OWNER/ringed_all_purpose_softbait_hook.gif</v>
+      </c>
+      <c r="I35" t="str">
+        <v/>
+      </c>
+      <c r="J35" t="str">
+        <v/>
+      </c>
+      <c r="K35" t="str">
+        <v>RINGED ALL PURPOSE SOFT BAIT HOOKS -This enhanced version of the famous 5108 All Purpose Soft Bait Hook features a welded ring, providing more natural bait movement and flutter. The 5108R is deadly effective for Free Rig techniques, Jika Rigs, Tokyo Rigs and beyond. Key features include: RINGED to provide extra free, natural bait movement [&amp;hellip;]</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>OHK1003</v>
+      </c>
+      <c r="B36">
+        <v>46</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Haymaker</v>
+      </c>
+      <c r="D36" t="str">
+        <v/>
+      </c>
+      <c r="E36" t="str">
+        <v/>
+      </c>
+      <c r="F36" t="str">
+        <v/>
+      </c>
+      <c r="G36" t="str">
+        <v>曲柄钩 / Offset / Wide Gap</v>
+      </c>
+      <c r="H36" t="str">
+        <v>pkgGear/images/hook/OWNER/haymaker.gif</v>
+      </c>
+      <c r="I36" t="str">
+        <v/>
+      </c>
+      <c r="J36" t="str">
+        <v/>
+      </c>
+      <c r="K36" t="str">
+        <v>Haymaker is truly a one-of-a-kind design. The extra wide gap can accommodate any soft bait, for any presentation. The angled-up Super Needle Point fishes like a straight shank hook-in perfect position for a quick, powerful hookset. Features a Silky Gray, frictionless finish that encourages superior hook penetration. XXX-Strong and available in sizes 1/0-5/0.</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>OHK1004</v>
+      </c>
+      <c r="B37">
+        <v>46</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Offset Shank, Wide Gap - Red</v>
+      </c>
+      <c r="D37" t="str">
+        <v/>
+      </c>
+      <c r="E37" t="str">
+        <v/>
+      </c>
+      <c r="F37" t="str">
+        <v/>
+      </c>
+      <c r="G37" t="str">
+        <v>曲柄钩 / Offset / Wide Gap</v>
+      </c>
+      <c r="H37" t="str">
+        <v>pkgGear/images/hook/OWNER/offset_shank_wide_gap_red.jpg</v>
+      </c>
+      <c r="I37" t="str">
+        <v/>
+      </c>
+      <c r="J37" t="str">
+        <v/>
+      </c>
+      <c r="K37" t="str">
+        <v>Offset Shank, Wide Gap worm hooks with worm-holding 90° bend shoulder. Extra wide gap bend and heavy-duty XX strong shank for rigging big baits and hauling bass from heavy cover. Ideal for jerk baits. Features include Cutting Point® and available in Black Chrome and Red finishes.</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>OHK1005</v>
+      </c>
+      <c r="B38">
+        <v>46</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Flashy Swimmer - Silver Colorado</v>
+      </c>
+      <c r="D38" t="str">
+        <v/>
+      </c>
+      <c r="E38" t="str">
+        <v/>
+      </c>
+      <c r="F38" t="str">
+        <v/>
+      </c>
+      <c r="G38" t="str">
+        <v>特种钩 / Swimbait</v>
+      </c>
+      <c r="H38" t="str">
+        <v>pkgGear/images/hook/OWNER/flashy_swimmer_silver_colorado.jpg</v>
+      </c>
+      <c r="I38" t="str">
+        <v/>
+      </c>
+      <c r="J38" t="str">
+        <v/>
+      </c>
+      <c r="K38" t="str">
+        <v>FLASHY SWIMMER with Owner's TwistLOCK™ Centering-Pin Spring (CPS-patent pending) is a unique setup for rigging soft swimbaits, flukes, and oth&amp;#8230;</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>OHK1006</v>
+      </c>
+      <c r="B39">
+        <v>46</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Flashy Swimmer - Gold WillowLeaf</v>
+      </c>
+      <c r="D39" t="str">
+        <v/>
+      </c>
+      <c r="E39" t="str">
+        <v/>
+      </c>
+      <c r="F39" t="str">
+        <v/>
+      </c>
+      <c r="G39" t="str">
+        <v>特种钩 / Swimbait</v>
+      </c>
+      <c r="H39" t="str">
+        <v>pkgGear/images/hook/OWNER/flashy_swimmer_gold_willowleaf.jpg</v>
+      </c>
+      <c r="I39" t="str">
+        <v/>
+      </c>
+      <c r="J39" t="str">
+        <v/>
+      </c>
+      <c r="K39" t="str">
+        <v>FLASHY SWIMMER with Owner's TwistLOCK™ Centering-Pin Spring (CPS-patent pending) is a unique setup for rigging soft swimbaits, flukes, and oth&amp;#8230;</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>OHK1007</v>
+      </c>
+      <c r="B40">
+        <v>46</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Jungle Flipping HD</v>
+      </c>
+      <c r="D40" t="str">
+        <v/>
+      </c>
+      <c r="E40" t="str">
+        <v/>
+      </c>
+      <c r="F40" t="str">
+        <v/>
+      </c>
+      <c r="G40" t="str">
+        <v>特种钩 / Bass Hook</v>
+      </c>
+      <c r="H40" t="str">
+        <v>pkgGear/images/hook/OWNER/jungle_flipping_hd.gif</v>
+      </c>
+      <c r="I40" t="str">
+        <v/>
+      </c>
+      <c r="J40" t="str">
+        <v/>
+      </c>
+      <c r="K40" t="str">
+        <v>Designed to be the baddest Flipping Hook on the market! You can have 100% confidence when flipping into the thickest of cover and catching the biggest of fish. 5X strong and comes with a welded eye to hold up with to strongest of braids. The bait keeper is doubled up for extra strength, welded to [&amp;hellip;]</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>OHK1008</v>
+      </c>
+      <c r="B41">
+        <v>46</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Cover Shot HD</v>
+      </c>
+      <c r="D41" t="str">
+        <v/>
+      </c>
+      <c r="E41" t="str">
+        <v/>
+      </c>
+      <c r="F41" t="str">
+        <v/>
+      </c>
+      <c r="G41" t="str">
+        <v>倒钓钩 / Drop Shot</v>
+      </c>
+      <c r="H41" t="str">
+        <v>pkgGear/images/hook/OWNER/cover_shot_hd.gif</v>
+      </c>
+      <c r="I41" t="str">
+        <v/>
+      </c>
+      <c r="J41" t="str">
+        <v/>
+      </c>
+      <c r="K41" t="str">
+        <v>A heavier version of Owner’s light wire Cover Shot. A little stouter to handle bigger fish, bigger baits, and heavy cover. Ideal for versatile uses including drop shot and Texas Rigging. The bait keeper is meticulously wrapped onto the shank to prevent the keeper from sliding or spinning. The monofilament keeper allows soft, supple baits [&amp;hellip;]</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>OHK1009</v>
+      </c>
+      <c r="B42">
+        <v>46</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Sniper Finesse</v>
+      </c>
+      <c r="D42" t="str">
+        <v/>
+      </c>
+      <c r="E42" t="str">
+        <v/>
+      </c>
+      <c r="F42" t="str">
+        <v/>
+      </c>
+      <c r="G42" t="str">
+        <v>曲柄钩 / Offset / Wide Gap</v>
+      </c>
+      <c r="H42" t="str">
+        <v>pkgGear/images/hook/OWNER/sniper_finesse.gif</v>
+      </c>
+      <c r="I42" t="str">
+        <v/>
+      </c>
+      <c r="J42" t="str">
+        <v/>
+      </c>
+      <c r="K42" t="str">
+        <v>Designed for Neko Style fishing, this hook comes in a standard version and a weedless version with Titanium weedguards. Hook includes a long shank with an offset point for better hooksets. Features Silky Gray finish Super Needle Point, and a 100% closed eye for braid applications.</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>OHK1010</v>
+      </c>
+      <c r="B43">
+        <v>46</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Jungle Wacky</v>
+      </c>
+      <c r="D43" t="str">
+        <v/>
+      </c>
+      <c r="E43" t="str">
+        <v/>
+      </c>
+      <c r="F43" t="str">
+        <v/>
+      </c>
+      <c r="G43" t="str">
+        <v>倒钓钩 / Wacky</v>
+      </c>
+      <c r="H43" t="str">
+        <v>pkgGear/images/hook/OWNER/jungle_wacky.gif</v>
+      </c>
+      <c r="I43" t="str">
+        <v/>
+      </c>
+      <c r="J43" t="str">
+        <v/>
+      </c>
+      <c r="K43" t="str">
+        <v>Includes a short shank and monster gap for superior hooking abilities. Made from Zo-Wire™ which makes hooks 15% stronger by diameter over other high carbon steel hooks. Also includes Silky Gray finish for superior penetration and Titanium weedguards for weedless presentations. Also Available in a non-weedguard series.</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>OHK1011</v>
+      </c>
+      <c r="B44">
+        <v>46</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Flashy Swimmer - Gold Colorado</v>
+      </c>
+      <c r="D44" t="str">
+        <v/>
+      </c>
+      <c r="E44" t="str">
+        <v/>
+      </c>
+      <c r="F44" t="str">
+        <v/>
+      </c>
+      <c r="G44" t="str">
+        <v>特种钩 / Swimbait</v>
+      </c>
+      <c r="H44" t="str">
+        <v>pkgGear/images/hook/OWNER/flashy_swimmer_gold_colorado.gif</v>
+      </c>
+      <c r="I44" t="str">
+        <v/>
+      </c>
+      <c r="J44" t="str">
+        <v/>
+      </c>
+      <c r="K44" t="str">
+        <v>FLASHY SWIMMER with Owner's TwistLOCK™ Centering-Pin Spring (CPS-patent pending) is a unique setup for rigging soft swimbaits, flukes, and oth&amp;#8230;</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>OHK1012</v>
+      </c>
+      <c r="B45">
+        <v>46</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Jungle Wide Gap</v>
+      </c>
+      <c r="D45" t="str">
+        <v/>
+      </c>
+      <c r="E45" t="str">
+        <v/>
+      </c>
+      <c r="F45" t="str">
+        <v/>
+      </c>
+      <c r="G45" t="str">
+        <v>曲柄钩 / Offset / Wide Gap</v>
+      </c>
+      <c r="H45" t="str">
+        <v>pkgGear/images/hook/OWNER/jungle_wide_gap.gif</v>
+      </c>
+      <c r="I45" t="str">
+        <v/>
+      </c>
+      <c r="J45" t="str">
+        <v/>
+      </c>
+      <c r="K45" t="str">
+        <v>One of the strongest Bass hooks on the market, 4X-Strong. This hook was designed with a few things in mind, heavy braided line and big baits. Made from Zo-Wire which is stronger than other traditional high carbon steel wires. With the point riding slightly above the eye, this is a true weedless hook. Can be [&amp;hellip;]</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>OHK1013</v>
+      </c>
+      <c r="B46">
+        <v>46</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Cover Shot</v>
+      </c>
+      <c r="D46" t="str">
+        <v/>
+      </c>
+      <c r="E46" t="str">
+        <v/>
+      </c>
+      <c r="F46" t="str">
+        <v/>
+      </c>
+      <c r="G46" t="str">
+        <v>倒钓钩 / Drop Shot</v>
+      </c>
+      <c r="H46" t="str">
+        <v>pkgGear/images/hook/OWNER/cover_shot.gif</v>
+      </c>
+      <c r="I46" t="str">
+        <v/>
+      </c>
+      <c r="J46" t="str">
+        <v/>
+      </c>
+      <c r="K46" t="str">
+        <v>A light finesse style hook for rigging small worms and baits. Typically used as a drop shot hook, this hook is made from fine wire for easy hooksets with light lines. The bait keeper is meticulously wrapped onto the shank to prevent the keeper from sliding or spinning. The monofilament keeper allows soft, supple baits [&amp;hellip;]</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>OHK1014</v>
+      </c>
+      <c r="B47">
+        <v>46</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Offset Shank, Wide Gap</v>
+      </c>
+      <c r="D47" t="str">
+        <v/>
+      </c>
+      <c r="E47" t="str">
+        <v/>
+      </c>
+      <c r="F47" t="str">
+        <v/>
+      </c>
+      <c r="G47" t="str">
+        <v>曲柄钩 / Offset / Wide Gap</v>
+      </c>
+      <c r="H47" t="str">
+        <v>pkgGear/images/hook/OWNER/offset_shank_wide_gap.jpg</v>
+      </c>
+      <c r="I47" t="str">
+        <v/>
+      </c>
+      <c r="J47" t="str">
+        <v/>
+      </c>
+      <c r="K47" t="str">
+        <v>Offset Shank, Wide Gap worm hooks with worm-holding 90° bend shoulder. Extra wide gap bend and heavy-duty XX strong shank for rigging big baits and hauling bass from heavy cover. Ideal for jerk baits. Features include Cutting Point® and available in Black Chrome and Red finishes.</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>OHK1015</v>
+      </c>
+      <c r="B48">
+        <v>46</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Toad Hook</v>
+      </c>
+      <c r="D48" t="str">
+        <v/>
+      </c>
+      <c r="E48" t="str">
+        <v/>
+      </c>
+      <c r="F48" t="str">
+        <v/>
+      </c>
+      <c r="G48" t="str">
+        <v>特种钩 / Bass Hook</v>
+      </c>
+      <c r="H48" t="str">
+        <v>pkgGear/images/hook/OWNER/toad_hook.jpg</v>
+      </c>
+      <c r="I48" t="str">
+        <v/>
+      </c>
+      <c r="J48" t="str">
+        <v/>
+      </c>
+      <c r="K48" t="str">
+        <v>The Double Toad hook was designed to be fished with any of the toad softbaits on the market. The hook is made from three separate pieces of wire, which makes it 100% balanced, unlike double hooks made from 2 pieces of the wire. A narrower V-angle between shanks rigs most "toads" perfectly and makes it [&amp;hellip;]</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>OHK1016</v>
+      </c>
+      <c r="B49">
+        <v>46</v>
+      </c>
+      <c r="C49" t="str">
+        <v>Wide Gap Plus</v>
+      </c>
+      <c r="D49" t="str">
+        <v/>
+      </c>
+      <c r="E49" t="str">
+        <v/>
+      </c>
+      <c r="F49" t="str">
+        <v/>
+      </c>
+      <c r="G49" t="str">
+        <v>曲柄钩 / Offset / Wide Gap</v>
+      </c>
+      <c r="H49" t="str">
+        <v>pkgGear/images/hook/OWNER/wide_gap_plus.jpg</v>
+      </c>
+      <c r="I49" t="str">
+        <v/>
+      </c>
+      <c r="J49" t="str">
+        <v/>
+      </c>
+      <c r="K49" t="str">
+        <v>Wide Gap Plus™, with its deep throat and dramatically elevated point, offers an extraordinary wide gap for extra hooking power. The plus point rides above the eye, providing a more positive and effective hook set. Ideal for weedless style Carolina Rig'N and Texas Rig'N of big tube baits and extra beefy soft plastic. Features include [&amp;hellip;]</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>OHK1017</v>
+      </c>
+      <c r="B50">
+        <v>46</v>
+      </c>
+      <c r="C50" t="str">
+        <v>Stinger Harness Rig</v>
+      </c>
+      <c r="D50" t="str">
+        <v/>
+      </c>
+      <c r="E50" t="str">
+        <v/>
+      </c>
+      <c r="F50" t="str">
+        <v/>
+      </c>
+      <c r="G50" t="str">
+        <v>特种钩 / Bass Hook</v>
+      </c>
+      <c r="H50" t="str">
+        <v>pkgGear/images/hook/OWNER/stinger_harness_rig.gif</v>
+      </c>
+      <c r="I50" t="str">
+        <v/>
+      </c>
+      <c r="J50" t="str">
+        <v/>
+      </c>
+      <c r="K50" t="str">
+        <v>This is the ultimate stinger harness rig, designed for use with both soft plastic and natural baits to eliminate short strikes and improve hookup ratio. Available in two models, each rig features a length of super tough 80-lb. braided line, terminating at one end with a large loop and at the other with our EZ-Snap [&amp;hellip;]</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>OHK1018</v>
+      </c>
+      <c r="B51">
+        <v>46</v>
+      </c>
+      <c r="C51" t="str">
+        <v>Twistlock Light - Weighted</v>
+      </c>
+      <c r="D51" t="str">
+        <v/>
+      </c>
+      <c r="E51" t="str">
+        <v/>
+      </c>
+      <c r="F51" t="str">
+        <v/>
+      </c>
+      <c r="G51" t="str">
+        <v>特种钩 / Bass Hook</v>
+      </c>
+      <c r="H51" t="str">
+        <v>pkgGear/images/hook/OWNER/twistlock_light_weighted.jpg</v>
+      </c>
+      <c r="I51" t="str">
+        <v/>
+      </c>
+      <c r="J51" t="str">
+        <v/>
+      </c>
+      <c r="K51" t="str">
+        <v>The weighted version not only helps sink or "swim" a rigged bait down into the strike zone, but helps to increase casting distance. The weight is positioned low on the shank to provide a keel" effect so that baits rigged weedless-style will swim naturally (as opposed to rolling or flipping when weights are inserted inside [&amp;hellip;]</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>OHK1019</v>
+      </c>
+      <c r="B52">
+        <v>46</v>
+      </c>
+      <c r="C52" t="str">
+        <v>J Light</v>
+      </c>
+      <c r="D52" t="str">
+        <v/>
+      </c>
+      <c r="E52" t="str">
+        <v/>
+      </c>
+      <c r="F52" t="str">
+        <v/>
+      </c>
+      <c r="G52" t="str">
+        <v>曲柄钩 / Offset / Wide Gap</v>
+      </c>
+      <c r="H52" t="str">
+        <v>pkgGear/images/hook/OWNER/j_light.gif</v>
+      </c>
+      <c r="I52" t="str">
+        <v/>
+      </c>
+      <c r="J52" t="str">
+        <v/>
+      </c>
+      <c r="K52" t="str">
+        <v>Patterned after the popular J Hook, the lighter wire provides easier hook-sets with less force. Ideal for Carolina and Texas rigging large profile soft plastic baits. Point surfaces quicker on hooksets, and wide bend reduces the chance of fish throwing the hook. Features include a Black Chrome finish, Super Needle Point and worm-holding Z-Lock shoulder [&amp;hellip;]</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>OHK1020</v>
+      </c>
+      <c r="B53">
+        <v>46</v>
+      </c>
+      <c r="C53" t="str">
+        <v>Rig'n Hook</v>
+      </c>
+      <c r="D53" t="str">
+        <v/>
+      </c>
+      <c r="E53" t="str">
+        <v/>
+      </c>
+      <c r="F53" t="str">
+        <v/>
+      </c>
+      <c r="G53" t="str">
+        <v>特种钩 / Bass Hook</v>
+      </c>
+      <c r="H53" t="str">
+        <v>pkgGear/images/hook/OWNER/rig_n_hook.jpg</v>
+      </c>
+      <c r="I53" t="str">
+        <v/>
+      </c>
+      <c r="J53" t="str">
+        <v/>
+      </c>
+      <c r="K53" t="str">
+        <v>RIG'N™ HOOKS, engineered for Carolina Rig'n, Texas Rig'n and Split Shot'n, ride with the point upright in an optimum striking position. Features include a short shank, huge wide bite with open gap, Cutting Point® and black chrome finish.</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>OHK1021</v>
+      </c>
+      <c r="B54">
+        <v>46</v>
+      </c>
+      <c r="C54" t="str">
+        <v>Wacky Hook</v>
+      </c>
+      <c r="D54" t="str">
+        <v/>
+      </c>
+      <c r="E54" t="str">
+        <v/>
+      </c>
+      <c r="F54" t="str">
+        <v/>
+      </c>
+      <c r="G54" t="str">
+        <v>倒钓钩 / Wacky</v>
+      </c>
+      <c r="H54" t="str">
+        <v>pkgGear/images/hook/OWNER/wacky_hook.jpg</v>
+      </c>
+      <c r="I54" t="str">
+        <v/>
+      </c>
+      <c r="J54" t="str">
+        <v/>
+      </c>
+      <c r="K54" t="str">
+        <v>Wacky Hooks, available with or without a weed-guard, are the perfect hook for down-shotting and drop-shotting natural baits and soft plastics for suspended bass and panfish. The hook gap's sharp-angle bend serves as a saddle that encourages a worm rigged at the middle to seek an optimum position for an enticing horizontal presentation, which makes [&amp;hellip;]</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>OHK1022</v>
+      </c>
+      <c r="B55">
+        <v>46</v>
+      </c>
+      <c r="C55" t="str">
+        <v>Twistlock 3X - Weighted</v>
+      </c>
+      <c r="D55" t="str">
+        <v/>
+      </c>
+      <c r="E55" t="str">
+        <v/>
+      </c>
+      <c r="F55" t="str">
+        <v/>
+      </c>
+      <c r="G55" t="str">
+        <v>特种钩 / Bass Hook</v>
+      </c>
+      <c r="H55" t="str">
+        <v>pkgGear/images/hook/OWNER/twistlock_3x_weighted.jpg</v>
+      </c>
+      <c r="I55" t="str">
+        <v/>
+      </c>
+      <c r="J55" t="str">
+        <v/>
+      </c>
+      <c r="K55" t="str">
+        <v>This Weighted Twistlock™ hook employs the same hook as the 5132 Twistlock™, but also features a non-movable weight attached to the shank. Designed for both fresh and saltwater fishing. The hook's added weight helps to sink or swim the bait into the strike zone. With its Twistlock™ Centering-Pin-Spring (CPS Patened), baits can be permanently secured [&amp;hellip;]</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>OHK1023</v>
+      </c>
+      <c r="B56">
+        <v>46</v>
+      </c>
+      <c r="C56" t="str">
+        <v>Twistlock 3X</v>
+      </c>
+      <c r="D56" t="str">
+        <v/>
+      </c>
+      <c r="E56" t="str">
+        <v/>
+      </c>
+      <c r="F56" t="str">
+        <v/>
+      </c>
+      <c r="G56" t="str">
+        <v>特种钩 / Bass Hook</v>
+      </c>
+      <c r="H56" t="str">
+        <v>pkgGear/images/hook/OWNER/twistlock_3x.jpg</v>
+      </c>
+      <c r="I56" t="str">
+        <v/>
+      </c>
+      <c r="J56" t="str">
+        <v/>
+      </c>
+      <c r="K56" t="str">
+        <v>This bass hook is Unique with its TwistLOCK™ Centering-Pin Spring (Patented) attached to the hook eye. Baits can be permanently secured by inserting the pin in the center of the nose of a soft plastic, which can then be twisted (screwed) onto the TwistLOCK™ coil spring so that any bait will rig perfectly everytime! The [&amp;hellip;]</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>OHK1024</v>
+      </c>
+      <c r="B57">
+        <v>46</v>
+      </c>
+      <c r="C57" t="str">
+        <v>Beast - Weighted</v>
+      </c>
+      <c r="D57" t="str">
+        <v/>
+      </c>
+      <c r="E57" t="str">
+        <v/>
+      </c>
+      <c r="F57" t="str">
+        <v/>
+      </c>
+      <c r="G57" t="str">
+        <v>特种钩 / Swimbait</v>
+      </c>
+      <c r="H57" t="str">
+        <v>pkgGear/images/hook/OWNER/beast_weighted.jpg</v>
+      </c>
+      <c r="I57" t="str">
+        <v/>
+      </c>
+      <c r="J57" t="str">
+        <v/>
+      </c>
+      <c r="K57" t="str">
+        <v>Beast Hooks with TwistLOCK® Centering-Pin Spring (CPS) are designed for weedless-style rigging of larger plastics like big swimbaits, flukes, tubes and creature baits. With its TwistLOCK® Centering-Pin Spring (CPS - patent pending) attached to the hook eye, baits can be permanently secured by inserting the pin in the center of the nose of a soft [&amp;hellip;]</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>OHK1025</v>
+      </c>
+      <c r="B58">
+        <v>46</v>
+      </c>
+      <c r="C58" t="str">
+        <v>Beast Hook</v>
+      </c>
+      <c r="D58" t="str">
+        <v/>
+      </c>
+      <c r="E58" t="str">
+        <v/>
+      </c>
+      <c r="F58" t="str">
+        <v/>
+      </c>
+      <c r="G58" t="str">
+        <v>特种钩 / Swimbait</v>
+      </c>
+      <c r="H58" t="str">
+        <v>pkgGear/images/hook/OWNER/beast_hook.jpg</v>
+      </c>
+      <c r="I58" t="str">
+        <v/>
+      </c>
+      <c r="J58" t="str">
+        <v/>
+      </c>
+      <c r="K58" t="str">
+        <v>This unweighted version has all the features of the Weighted Beast less the weight. The unweighted version is ideal for lighter baits than do not need large amounts of weight to be swam. Due the XXX-strong wire and big gap angle there is a lot of steel in this hook which allows the hook alone [&amp;hellip;]</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>OHK1026</v>
+      </c>
+      <c r="B59">
+        <v>46</v>
+      </c>
+      <c r="C59" t="str">
+        <v>Flashy Swimmer - Beast Version</v>
+      </c>
+      <c r="D59" t="str">
+        <v/>
+      </c>
+      <c r="E59" t="str">
+        <v/>
+      </c>
+      <c r="F59" t="str">
+        <v/>
+      </c>
+      <c r="G59" t="str">
+        <v>特种钩 / Swimbait</v>
+      </c>
+      <c r="H59" t="str">
+        <v>pkgGear/images/hook/OWNER/flashy_swimmer_beast_version.gif</v>
+      </c>
+      <c r="I59" t="str">
+        <v/>
+      </c>
+      <c r="J59" t="str">
+        <v/>
+      </c>
+      <c r="K59" t="str">
+        <v>FLASHY SWIMMER - Beast Verion Owner's TwistLOCK Centering-Pin Spring (CPS-patent pending) is a unique setup for rigging soft swimbaits, flukes, and other swimming plastics. The spinner blade is attached to a non-moveable weight that keels a rigged soft plastic perfectly for use as an ideal "search" bait. In lieu of spinnerbaits or crankbaits, the flashy [&amp;hellip;]</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>OHK1027</v>
+      </c>
+      <c r="B60">
+        <v>46</v>
+      </c>
+      <c r="C60" t="str">
+        <v>Twistlock Light</v>
+      </c>
+      <c r="D60" t="str">
+        <v/>
+      </c>
+      <c r="E60" t="str">
+        <v/>
+      </c>
+      <c r="F60" t="str">
+        <v/>
+      </c>
+      <c r="G60" t="str">
+        <v>特种钩 / Bass Hook</v>
+      </c>
+      <c r="H60" t="str">
+        <v>pkgGear/images/hook/OWNER/twistlock_light.jpg</v>
+      </c>
+      <c r="I60" t="str">
+        <v/>
+      </c>
+      <c r="J60" t="str">
+        <v/>
+      </c>
+      <c r="K60" t="str">
+        <v>TwistLOCK Light with Centering-Pin Spring (CPS-patent pending) is a lighter version of our TwistLOCK bass hook. With guidance from bass fishing professional and lure designer Gary Yamamoto, the TwistLOCK Light was created as the ideal hook for rigging Senko-style baits and other thinner profile plastics. With Owner's unique "Centering-Pin Spring" (CPS - patent pending) attached [&amp;hellip;]</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>OHK1028</v>
+      </c>
+      <c r="B61">
+        <v>46</v>
+      </c>
+      <c r="C61" t="str">
+        <v>Twistlock Flipping Hook</v>
+      </c>
+      <c r="D61" t="str">
+        <v/>
+      </c>
+      <c r="E61" t="str">
+        <v/>
+      </c>
+      <c r="F61" t="str">
+        <v/>
+      </c>
+      <c r="G61" t="str">
+        <v>特种钩 / Bass Hook</v>
+      </c>
+      <c r="H61" t="str">
+        <v>pkgGear/images/hook/OWNER/twistlock_flipping_hook.jpg</v>
+      </c>
+      <c r="I61" t="str">
+        <v/>
+      </c>
+      <c r="J61" t="str">
+        <v/>
+      </c>
+      <c r="K61" t="str">
+        <v>The Twistlock Flipping Hook is a revolutionary new flipping hook. While traditional flipping hooks have straight shanks and tedious methods of securing bait heads to the shank, the TFH takes this category to a whole new level. With the patent pending CPS (Centering Pin Spring), baits can be rigged quickly and perfectly straight with no [&amp;hellip;]</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>OHK1029</v>
+      </c>
+      <c r="B62">
+        <v>46</v>
+      </c>
+      <c r="C62" t="str">
+        <v>All Purpose Softbait Hook</v>
+      </c>
+      <c r="D62" t="str">
+        <v/>
+      </c>
+      <c r="E62" t="str">
+        <v/>
+      </c>
+      <c r="F62" t="str">
+        <v/>
+      </c>
+      <c r="G62" t="str">
+        <v>曲柄钩 / Offset / Wide Gap</v>
+      </c>
+      <c r="H62" t="str">
+        <v>pkgGear/images/hook/OWNER/all_purpose_softbait_hook.jpg</v>
+      </c>
+      <c r="I62" t="str">
+        <v/>
+      </c>
+      <c r="J62" t="str">
+        <v/>
+      </c>
+      <c r="K62" t="str">
+        <v>All Purpose Soft Bait Hooks have an extra wide gap that will accommodate thicker soft plastic baits for weedless rigging. Rated X-strong, and features include a Z-lock shoulder bend, Super Needle Point and black chrome finish.</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>OHK1030</v>
+      </c>
+      <c r="B63">
+        <v>46</v>
+      </c>
+      <c r="C63" t="str">
+        <v>All Purpose Worm Hook</v>
+      </c>
+      <c r="D63" t="str">
+        <v/>
+      </c>
+      <c r="E63" t="str">
+        <v/>
+      </c>
+      <c r="F63" t="str">
+        <v/>
+      </c>
+      <c r="G63" t="str">
+        <v>曲柄钩 / Offset / Wide Gap</v>
+      </c>
+      <c r="H63" t="str">
+        <v>pkgGear/images/hook/OWNER/all_purpose_worm_hook.gif</v>
+      </c>
+      <c r="I63" t="str">
+        <v/>
+      </c>
+      <c r="J63" t="str">
+        <v/>
+      </c>
+      <c r="K63" t="str">
+        <v>All Purpose Worm Hooks, can be used for rigging almost any type of plastic worm. Rated X-strong, and a Z-lock shoulder bend makes for quick rigging and holds the worm head up by the eye. Features include a round bend, super Needle Point and black chrome finish.</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>OHK1031</v>
+      </c>
+      <c r="B64">
+        <v>46</v>
+      </c>
+      <c r="C64" t="str">
+        <v>Jungle Flipping Hook</v>
+      </c>
+      <c r="D64" t="str">
+        <v/>
+      </c>
+      <c r="E64" t="str">
+        <v/>
+      </c>
+      <c r="F64" t="str">
+        <v/>
+      </c>
+      <c r="G64" t="str">
+        <v>特种钩 / Bass Hook</v>
+      </c>
+      <c r="H64" t="str">
+        <v>pkgGear/images/hook/OWNER/jungle_flipping_hook.gif</v>
+      </c>
+      <c r="I64" t="str">
+        <v/>
+      </c>
+      <c r="J64" t="str">
+        <v/>
+      </c>
+      <c r="K64" t="str">
+        <v>The Jungle Flipping Hook was designed to withstand heavy braided line use and the toughest of conditions. Made with Zo-Wire™, the wire strength is stronger than other traditional high carbon steel wires. This means smaller hook wire diameters for better penetration and a Super Needle Point that will not roll over or dull. The eye [&amp;hellip;]</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>OHK1032</v>
+      </c>
+      <c r="B65">
+        <v>46</v>
+      </c>
+      <c r="C65" t="str">
+        <v>Oversize Worm Hook</v>
+      </c>
+      <c r="D65" t="str">
+        <v/>
+      </c>
+      <c r="E65" t="str">
+        <v/>
+      </c>
+      <c r="F65" t="str">
+        <v/>
+      </c>
+      <c r="G65" t="str">
+        <v>曲柄钩 / Offset / Wide Gap</v>
+      </c>
+      <c r="H65" t="str">
+        <v>pkgGear/images/hook/OWNER/oversize_worm_hook.jpg</v>
+      </c>
+      <c r="I65" t="str">
+        <v/>
+      </c>
+      <c r="J65" t="str">
+        <v/>
+      </c>
+      <c r="K65" t="str">
+        <v>Oversize worm hook, with a heavy-duty forged shank, is the ideal choice for rigging king-size worms for big bass. Features include worm holdin&amp;#8230;</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>OHK1033</v>
+      </c>
+      <c r="B66">
+        <v>46</v>
+      </c>
+      <c r="C66" t="str">
+        <v>J Hook</v>
+      </c>
+      <c r="D66" t="str">
+        <v/>
+      </c>
+      <c r="E66" t="str">
+        <v/>
+      </c>
+      <c r="F66" t="str">
+        <v/>
+      </c>
+      <c r="G66" t="str">
+        <v>曲柄钩 / Offset / Wide Gap</v>
+      </c>
+      <c r="H66" t="str">
+        <v>pkgGear/images/hook/OWNER/j_hook.jpg</v>
+      </c>
+      <c r="I66" t="str">
+        <v/>
+      </c>
+      <c r="J66" t="str">
+        <v/>
+      </c>
+      <c r="K66" t="str">
+        <v>JigRig Offset Hookis the same hook used with the JigRig. Features an extra wide gap, Z-Lock shoulder bend, Super Needle Point, and black chro&amp;#8230;</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>OHK1034</v>
+      </c>
+      <c r="B67">
+        <v>46</v>
+      </c>
+      <c r="C67" t="str">
+        <v>Straight Shank, Wide Gap</v>
+      </c>
+      <c r="D67" t="str">
+        <v/>
+      </c>
+      <c r="E67" t="str">
+        <v/>
+      </c>
+      <c r="F67" t="str">
+        <v/>
+      </c>
+      <c r="G67" t="str">
+        <v>曲柄钩 / Offset / Wide Gap</v>
+      </c>
+      <c r="H67" t="str">
+        <v>pkgGear/images/hook/OWNER/straight_shank_wide_gap.jpg</v>
+      </c>
+      <c r="I67" t="str">
+        <v/>
+      </c>
+      <c r="J67" t="str">
+        <v/>
+      </c>
+      <c r="K67" t="str">
+        <v>Straight Shank, Wide Gap worm hooks for flipping and pitching large baits and setting the hook on big bass. Features include a round bend, Cut&amp;#8230;</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>OHK1035</v>
+      </c>
+      <c r="B68">
+        <v>46</v>
+      </c>
+      <c r="C68" t="str">
+        <v>Straight Shank</v>
+      </c>
+      <c r="D68" t="str">
+        <v/>
+      </c>
+      <c r="E68" t="str">
+        <v/>
+      </c>
+      <c r="F68" t="str">
+        <v/>
+      </c>
+      <c r="G68" t="str">
+        <v>曲柄钩 / Offset / Wide Gap</v>
+      </c>
+      <c r="H68" t="str">
+        <v>pkgGear/images/hook/OWNER/straight_shank.jpg</v>
+      </c>
+      <c r="I68" t="str">
+        <v/>
+      </c>
+      <c r="J68" t="str">
+        <v/>
+      </c>
+      <c r="K68" t="str">
+        <v>Straight Shank worm hooks, ideal for split-shotting plastic worms for wary bass. Features include a round bend, Cutting Point™, black chrome finish and baitholder slices on the inside of the straight shank.</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>OHK1036</v>
+      </c>
+      <c r="B69">
+        <v>46</v>
+      </c>
+      <c r="C69" t="str">
+        <v>Phantom Tube Hook</v>
+      </c>
+      <c r="D69" t="str">
+        <v/>
+      </c>
+      <c r="E69" t="str">
+        <v/>
+      </c>
+      <c r="F69" t="str">
+        <v/>
+      </c>
+      <c r="G69" t="str">
+        <v>特种钩 / Bass Hook</v>
+      </c>
+      <c r="H69" t="str">
+        <v>pkgGear/images/hook/OWNER/phantom_tube_hook.jpg</v>
+      </c>
+      <c r="I69" t="str">
+        <v/>
+      </c>
+      <c r="J69" t="str">
+        <v/>
+      </c>
+      <c r="K69" t="str">
+        <v>Phantom Tube Hook™ features a unique weighted system designed specifically for rigging tube and hollow baits weedless&amp;#8230;.</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>OHK1037</v>
+      </c>
+      <c r="B70">
+        <v>46</v>
+      </c>
+      <c r="C70" t="str">
+        <v>Mosquito Hook</v>
+      </c>
+      <c r="D70" t="str">
+        <v/>
+      </c>
+      <c r="E70" t="str">
+        <v/>
+      </c>
+      <c r="F70" t="str">
+        <v/>
+      </c>
+      <c r="G70" t="str">
+        <v>特种钩 / Bass Hook</v>
+      </c>
+      <c r="H70" t="str">
+        <v>pkgGear/images/hook/OWNER/mosquito_hook.gif</v>
+      </c>
+      <c r="I70" t="str">
+        <v/>
+      </c>
+      <c r="J70" t="str">
+        <v/>
+      </c>
+      <c r="K70" t="str">
+        <v>Fast becoming a favorite when using the down shot system for bass, walleye and panfish. For light line use, it is self-setting and the perfect&amp;#8230;</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>OHK1038</v>
+      </c>
+      <c r="B71">
+        <v>46</v>
+      </c>
+      <c r="C71" t="str">
+        <v>Offset Shank</v>
+      </c>
+      <c r="D71" t="str">
+        <v/>
+      </c>
+      <c r="E71" t="str">
+        <v/>
+      </c>
+      <c r="F71" t="str">
+        <v/>
+      </c>
+      <c r="G71" t="str">
+        <v>曲柄钩 / Offset / Wide Gap</v>
+      </c>
+      <c r="H71" t="str">
+        <v>pkgGear/images/hook/OWNER/offset_shank.jpg</v>
+      </c>
+      <c r="I71" t="str">
+        <v/>
+      </c>
+      <c r="J71" t="str">
+        <v/>
+      </c>
+      <c r="K71" t="str">
+        <v>Offset worm hooks, with a worm-holding 90 degree bend shoulder. Preferred by many anglers for straight and easy rigging of plastic worms. Feat&amp;#8230;</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>OHK1039</v>
+      </c>
+      <c r="B72">
+        <v>46</v>
+      </c>
+      <c r="C72" t="str">
+        <v>Flashy Swimmer - Silver WillowLeaf</v>
+      </c>
+      <c r="D72" t="str">
+        <v/>
+      </c>
+      <c r="E72" t="str">
+        <v/>
+      </c>
+      <c r="F72" t="str">
+        <v/>
+      </c>
+      <c r="G72" t="str">
+        <v>特种钩 / Swimbait</v>
+      </c>
+      <c r="H72" t="str">
+        <v>pkgGear/images/hook/OWNER/flashy_swimmer_silver_willowleaf.jpg</v>
+      </c>
+      <c r="I72" t="str">
+        <v/>
+      </c>
+      <c r="J72" t="str">
+        <v/>
+      </c>
+      <c r="K72" t="str">
+        <v>FLASHY SWIMMER with Owner's TwistLOCK™ Centering-Pin Spring (CPS-patent pending) is a unique setup for rigging soft swimbaits, flukes, and oth&amp;#8230;</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K32"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K72"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/GearSage-client/rate/excel/hook.xlsx
+++ b/GearSage-client/rate/excel/hook.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K72"/>
+  <dimension ref="A1:K116"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2919,9 +2919,1549 @@
         <v>FLASHY SWIMMER with Owner's TwistLOCK™ Centering-Pin Spring (CPS-patent pending) is a unique setup for rigging soft swimbaits, flukes, and oth&amp;#8230;</v>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>BHK1000</v>
+      </c>
+      <c r="B73">
+        <v>111</v>
+      </c>
+      <c r="C73" t="str">
+        <v>Predator WG Weedless</v>
+      </c>
+      <c r="D73" t="str">
+        <v/>
+      </c>
+      <c r="E73" t="str">
+        <v/>
+      </c>
+      <c r="F73" t="str">
+        <v/>
+      </c>
+      <c r="G73" t="str">
+        <v>wacky钩</v>
+      </c>
+      <c r="H73" t="str">
+        <v>pkgGear/images/hook/BKK/predator_wg_weedless.webp</v>
+      </c>
+      <c r="I73" t="str">
+        <v/>
+      </c>
+      <c r="J73" t="str">
+        <v/>
+      </c>
+      <c r="K73" t="str">
+        <v>The Predator WG Weedless is the weedless version of the original Predator WG for wacky and dropshot presentations. Featuring an SS finish and needle point for improved penetration performance and a forged shank, it is equipped with a fluorocarbon weed guard engineered to prevent the hook snagging the cover while allowing it to penetrate a fish with ease when striking. The guard is securely connected to the shank of the hook through strong binding thread further covered in epoxy-resin and will keep its shape and orientation fish after fish.</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>BHK1001</v>
+      </c>
+      <c r="B74">
+        <v>111</v>
+      </c>
+      <c r="C74" t="str">
+        <v>Heavy Cover</v>
+      </c>
+      <c r="D74" t="str">
+        <v/>
+      </c>
+      <c r="E74" t="str">
+        <v/>
+      </c>
+      <c r="F74" t="str">
+        <v/>
+      </c>
+      <c r="G74" t="str">
+        <v>直柄钩</v>
+      </c>
+      <c r="H74" t="str">
+        <v>pkgGear/images/hook/BKK/heavy_cover.webp</v>
+      </c>
+      <c r="I74" t="str">
+        <v/>
+      </c>
+      <c r="J74" t="str">
+        <v/>
+      </c>
+      <c r="K74" t="str">
+        <v>The BKK Heavy Cover is developed for flipping and punching techniques. This hook is equipped with an SS finish and an extra-short needle point to ensure an excellent penetration performance and an improved point strength.</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>BHK1002</v>
+      </c>
+      <c r="B75">
+        <v>111</v>
+      </c>
+      <c r="C75" t="str">
+        <v>DSS-Worm UVO</v>
+      </c>
+      <c r="D75" t="str">
+        <v/>
+      </c>
+      <c r="E75" t="str">
+        <v/>
+      </c>
+      <c r="F75" t="str">
+        <v/>
+      </c>
+      <c r="G75" t="str">
+        <v>倒钓钩</v>
+      </c>
+      <c r="H75" t="str">
+        <v>pkgGear/images/hook/BKK/dss_worm_uvo.webp</v>
+      </c>
+      <c r="I75" t="str">
+        <v/>
+      </c>
+      <c r="J75" t="str">
+        <v/>
+      </c>
+      <c r="K75" t="str">
+        <v>The BKK DSS – Worm UVO is the ultimate hook for a wide range of light-line tactics as dropshot and split shot. Features include a razor sharp needle point to ensure the best strike-to-land ratio, a forged shank for increased strength, and fluorescent UV coating for added attraction.</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>BHK1003</v>
+      </c>
+      <c r="B76">
+        <v>111</v>
+      </c>
+      <c r="C76" t="str">
+        <v>DSS-WORM</v>
+      </c>
+      <c r="D76" t="str">
+        <v/>
+      </c>
+      <c r="E76" t="str">
+        <v/>
+      </c>
+      <c r="F76" t="str">
+        <v/>
+      </c>
+      <c r="G76" t="str">
+        <v>倒钓钩</v>
+      </c>
+      <c r="H76" t="str">
+        <v>pkgGear/images/hook/BKK/dss_worm.webp</v>
+      </c>
+      <c r="I76" t="str">
+        <v/>
+      </c>
+      <c r="J76" t="str">
+        <v/>
+      </c>
+      <c r="K76" t="str">
+        <v>The BKK DSS WORM is the ultimate hook for a wide range of light-line tactics as dropsot and split shot. Features include a razor sharp needle point to ensure the best strike-to-land ratio, a forged shank for increased strength, and the super slick super slide coating for a smooth penetration.</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>BHK1004</v>
+      </c>
+      <c r="B77">
+        <v>111</v>
+      </c>
+      <c r="C77" t="str">
+        <v>Predator WG</v>
+      </c>
+      <c r="D77" t="str">
+        <v/>
+      </c>
+      <c r="E77" t="str">
+        <v/>
+      </c>
+      <c r="F77" t="str">
+        <v/>
+      </c>
+      <c r="G77" t="str">
+        <v>wacky钩</v>
+      </c>
+      <c r="H77" t="str">
+        <v>pkgGear/images/hook/BKK/predator_wg.webp</v>
+      </c>
+      <c r="I77" t="str">
+        <v/>
+      </c>
+      <c r="J77" t="str">
+        <v/>
+      </c>
+      <c r="K77" t="str">
+        <v>The BKK Predator WG is a freshwater finesse hook used for a variety of rigs such as wacky and dropshot, primarily for bass fishing. The wide-gap design and the super slide coating significantly enhance the hook-up rate, while the micro barb makes it suitable for catch and release. Despite its slim profile, the Predator WG is strong enough to fight big prey thanks to its forged shank.</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>BHK1005</v>
+      </c>
+      <c r="B78">
+        <v>111</v>
+      </c>
+      <c r="C78" t="str">
+        <v>Muse</v>
+      </c>
+      <c r="D78" t="str">
+        <v/>
+      </c>
+      <c r="E78" t="str">
+        <v/>
+      </c>
+      <c r="F78" t="str">
+        <v/>
+      </c>
+      <c r="G78" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="H78" t="str">
+        <v>pkgGear/images/hook/BKK/muse.webp</v>
+      </c>
+      <c r="I78" t="str">
+        <v/>
+      </c>
+      <c r="J78" t="str">
+        <v/>
+      </c>
+      <c r="K78" t="str">
+        <v>BKK Muse is a finesse worm hook designed for weed-less presentations of soft plastic baits when targeting fish in pressured fishing areas. The extra fine gauge wire makes it ideal for finesse or ultralight fishing applications such as texas rigging weightless senko, stick baits and ajing soft plastics. Furthermore, the combination of Super Slide coating and the in-turned needle-sharp hook point reduces the piercing resistance and provides great impaling power, increasing the overall penetration performance.</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>BHK1006</v>
+      </c>
+      <c r="B79">
+        <v>111</v>
+      </c>
+      <c r="C79" t="str">
+        <v>Nemesis</v>
+      </c>
+      <c r="D79" t="str">
+        <v/>
+      </c>
+      <c r="E79" t="str">
+        <v/>
+      </c>
+      <c r="F79" t="str">
+        <v/>
+      </c>
+      <c r="G79" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="H79" t="str">
+        <v>pkgGear/images/hook/BKK/nemesis.webp</v>
+      </c>
+      <c r="I79" t="str">
+        <v/>
+      </c>
+      <c r="J79" t="str">
+        <v/>
+      </c>
+      <c r="K79" t="str">
+        <v>The BKK Nemesis is designed to Texas rig bulkier profile soft plastic baits such as flukes and swimbaits. For such purpose, the hook has an extra wide gap design that makes sure there is enough room between the shank and the point to ease the hook set. Besides, the hook has a medium-light gauge that is specifically chosen to fit medium and light-weight lines. BKK’s needle sharp hook point and Super Slide coating provide an enhanced penetration performance by reducing the piercing resistance, thereby increasing the hook up ratio.</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>BHK1007</v>
+      </c>
+      <c r="B80">
+        <v>111</v>
+      </c>
+      <c r="C80" t="str">
+        <v>Chimera</v>
+      </c>
+      <c r="D80" t="str">
+        <v/>
+      </c>
+      <c r="E80" t="str">
+        <v/>
+      </c>
+      <c r="F80" t="str">
+        <v/>
+      </c>
+      <c r="G80" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="H80" t="str">
+        <v>pkgGear/images/hook/BKK/chimera.webp</v>
+      </c>
+      <c r="I80" t="str">
+        <v/>
+      </c>
+      <c r="J80" t="str">
+        <v/>
+      </c>
+      <c r="K80" t="str">
+        <v>The BKK Chimera is designed for Texas rigging creature baits such as crawls, and lizard-style baits. For this reason, the hook is designed with a wide gap that ensures adequate room between the shank and the hook tip, enhancing the hook up ratio. The medium-heavy gauge design is suitable for the use of medium-heavy lines. The hook comes with needle sharp hook point out of the package that delivers great penetration performance. Additionally, BKK’s Super Slide coating decreases piercing resistance, ensuring smooth hook ups.</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>BHK1008</v>
+      </c>
+      <c r="B81">
+        <v>111</v>
+      </c>
+      <c r="C81" t="str">
+        <v>Siren</v>
+      </c>
+      <c r="D81" t="str">
+        <v/>
+      </c>
+      <c r="E81" t="str">
+        <v/>
+      </c>
+      <c r="F81" t="str">
+        <v/>
+      </c>
+      <c r="G81" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="H81" t="str">
+        <v>pkgGear/images/hook/BKK/siren.webp</v>
+      </c>
+      <c r="I81" t="str">
+        <v/>
+      </c>
+      <c r="J81" t="str">
+        <v/>
+      </c>
+      <c r="K81" t="str">
+        <v>The BKK Siren is a worm hook specifically developed for Texas rigging a wide variety of worm baits such as curly tail worm baits, straight tail worm baits and stick baits. A medium gauge wire design makes it suitable for medium weight lines. The round bend ensures an adequate hook gap that allows for a proper hook up even when using bulkier profile worm baits. The combination of Super Slide coating and the needle-sharp hook point ensures great penetration performance and smooth hook ups by decreasing piercing resistance.</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>BHK1009</v>
+      </c>
+      <c r="B82">
+        <v>111</v>
+      </c>
+      <c r="C82" t="str">
+        <v>Basilisk</v>
+      </c>
+      <c r="D82" t="str">
+        <v/>
+      </c>
+      <c r="E82" t="str">
+        <v/>
+      </c>
+      <c r="F82" t="str">
+        <v/>
+      </c>
+      <c r="G82" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="H82" t="str">
+        <v>pkgGear/images/hook/BKK/basilisk.webp</v>
+      </c>
+      <c r="I82" t="str">
+        <v/>
+      </c>
+      <c r="J82" t="str">
+        <v/>
+      </c>
+      <c r="K82" t="str">
+        <v>The BKK Basilisk is designed for Texas-style rigging of slimmer profile worm baits such as curly tail worms and straight tail worms, fishing with medium-weight line. The traditional O’shaughnessy bend design prevents the fish from coming off during the fight, ensuring a solid hook up. In addition, BKK’s signature Super Slide hook coating and needle-sharp hook point provide excellent penetration performance, increasing the hook up ratio.</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>BHK1010</v>
+      </c>
+      <c r="B83">
+        <v>111</v>
+      </c>
+      <c r="C83" t="str">
+        <v>REFRAX Jighead</v>
+      </c>
+      <c r="D83" t="str">
+        <v/>
+      </c>
+      <c r="E83" t="str">
+        <v/>
+      </c>
+      <c r="F83" t="str">
+        <v/>
+      </c>
+      <c r="G83" t="str">
+        <v>铅头钩</v>
+      </c>
+      <c r="H83" t="str">
+        <v>pkgGear/images/hook/BKK/refrax_jighead.webp</v>
+      </c>
+      <c r="I83" t="str">
+        <v/>
+      </c>
+      <c r="J83" t="str">
+        <v/>
+      </c>
+      <c r="K83" t="str">
+        <v>High‑performance jighead with multifaceted profile and lifelike 3D holographic eyes to mimic baitfish. Dual‑wire bait keeper secures soft plastics without tearing. Built on Hyper Carbon Steel with Super Slide coating and an extra‑sharp needle point for smooth penetration and reliable hooksets. Weight and hook size stamped on the belly.</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>BHK1011</v>
+      </c>
+      <c r="B84">
+        <v>111</v>
+      </c>
+      <c r="C84" t="str">
+        <v>PRISMA DARTING</v>
+      </c>
+      <c r="D84" t="str">
+        <v/>
+      </c>
+      <c r="E84" t="str">
+        <v/>
+      </c>
+      <c r="F84" t="str">
+        <v/>
+      </c>
+      <c r="G84" t="str">
+        <v>铅头钩</v>
+      </c>
+      <c r="H84" t="str">
+        <v>pkgGear/images/hook/BKK/prisma_darting.webp</v>
+      </c>
+      <c r="I84" t="str">
+        <v/>
+      </c>
+      <c r="J84" t="str">
+        <v/>
+      </c>
+      <c r="K84" t="str">
+        <v>Designed for soft jerkbaits and pintails, the Silent Chaser Prisma Darting produces a sharp darting action to trigger open‑water strikes. Fitted with larger hooks for bigger bass and perch, it features ultra‑sharp needle points and a metal bait holder for secure rigging and fast bait changes. Versatile, durable, and built for authentic action.</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>BHK1012</v>
+      </c>
+      <c r="B85">
+        <v>111</v>
+      </c>
+      <c r="C85" t="str">
+        <v>HYPERLATCH ROUND HEAD TUNGSTEN</v>
+      </c>
+      <c r="D85" t="str">
+        <v/>
+      </c>
+      <c r="E85" t="str">
+        <v/>
+      </c>
+      <c r="F85" t="str">
+        <v/>
+      </c>
+      <c r="G85" t="str">
+        <v>铅头钩</v>
+      </c>
+      <c r="H85" t="str">
+        <v>pkgGear/images/hook/BKK/hyperlatch_round_head_tungsten.webp</v>
+      </c>
+      <c r="I85" t="str">
+        <v/>
+      </c>
+      <c r="J85" t="str">
+        <v/>
+      </c>
+      <c r="K85" t="str">
+        <v>High‑density tungsten jighead for heightened sensitivity and better sonar visibility. Laser‑welded bait holder secures soft plastics; Hyper Carbon Steel hook with Super Slide coating and ultra‑sharp point ensures strong, smooth penetration. Available in multiple weights and sizes, with size/weight stamped on the head for quick ID.</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>BHK1013</v>
+      </c>
+      <c r="B86">
+        <v>111</v>
+      </c>
+      <c r="C86" t="str">
+        <v>Hyperlatch round head</v>
+      </c>
+      <c r="D86" t="str">
+        <v/>
+      </c>
+      <c r="E86" t="str">
+        <v/>
+      </c>
+      <c r="F86" t="str">
+        <v/>
+      </c>
+      <c r="G86" t="str">
+        <v>铅头钩</v>
+      </c>
+      <c r="H86" t="str">
+        <v>pkgGear/images/hook/BKK/hyperlatch_round_head.webp</v>
+      </c>
+      <c r="I86" t="str">
+        <v/>
+      </c>
+      <c r="J86" t="str">
+        <v/>
+      </c>
+      <c r="K86" t="str">
+        <v>All‑round wide‑gap jighead for multiple species and soft plastics. Hyper Carbon Steel construction with Super Slide coating and needle point for strong, smooth penetration. Secure bait holder improves retention; available in many sizes and weights with markings on the head for quick ID.</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>BHK1014</v>
+      </c>
+      <c r="B87">
+        <v>111</v>
+      </c>
+      <c r="C87" t="str">
+        <v>Hyperlatch INSHORE</v>
+      </c>
+      <c r="D87" t="str">
+        <v/>
+      </c>
+      <c r="E87" t="str">
+        <v/>
+      </c>
+      <c r="F87" t="str">
+        <v/>
+      </c>
+      <c r="G87" t="str">
+        <v>铅头钩</v>
+      </c>
+      <c r="H87" t="str">
+        <v>pkgGear/images/hook/BKK/hyperlatch_inshore.webp</v>
+      </c>
+      <c r="I87" t="str">
+        <v/>
+      </c>
+      <c r="J87" t="str">
+        <v/>
+      </c>
+      <c r="K87" t="str">
+        <v>2X‑wire Hyper Carbon Steel jighead for inshore and freshwater predators. Wide‑gap bend and needle point for deep penetration; Hyperlatch keeper fits many softbaits. Super Slide coating for smooth hooksets; size and weight stamped on the head.</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>BHK1015</v>
+      </c>
+      <c r="B88">
+        <v>111</v>
+      </c>
+      <c r="C88" t="str">
+        <v>Hyperlatch Hidden Weight</v>
+      </c>
+      <c r="D88" t="str">
+        <v/>
+      </c>
+      <c r="E88" t="str">
+        <v/>
+      </c>
+      <c r="F88" t="str">
+        <v/>
+      </c>
+      <c r="G88" t="str">
+        <v>铅头钩</v>
+      </c>
+      <c r="H88" t="str">
+        <v>pkgGear/images/hook/BKK/hyperlatch_hidden_weight.webp</v>
+      </c>
+      <c r="I88" t="str">
+        <v/>
+      </c>
+      <c r="J88" t="str">
+        <v/>
+      </c>
+      <c r="K88" t="str">
+        <v>Hidden‑shank finesse jighead for a natural horizontal fall. Hyper Carbon Steel with Super Slide coating and needle point for strong, smooth hooksets. Hyperlatch keeper secures various softbaits; available in multiple sizes and weights.</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>BHK1016</v>
+      </c>
+      <c r="B89">
+        <v>111</v>
+      </c>
+      <c r="C89" t="str">
+        <v>Hyperlatch Barra Special</v>
+      </c>
+      <c r="D89" t="str">
+        <v/>
+      </c>
+      <c r="E89" t="str">
+        <v/>
+      </c>
+      <c r="F89" t="str">
+        <v/>
+      </c>
+      <c r="G89" t="str">
+        <v>铅头钩</v>
+      </c>
+      <c r="H89" t="str">
+        <v>pkgGear/images/hook/BKK/hyperlatch_barra_special.webp</v>
+      </c>
+      <c r="I89" t="str">
+        <v/>
+      </c>
+      <c r="J89" t="str">
+        <v/>
+      </c>
+      <c r="K89" t="str">
+        <v>2X‑wire heavy‑duty jighead for inshore predators. Hyper Carbon Steel with SS coating and ultra‑sharp point for reliable penetration. Wide gap and bait keeper fit most soft plastics; stainless assist eyelet accepts treble/assist hooks or blades. Size/weight stamped on head.</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>BHK1017</v>
+      </c>
+      <c r="B90">
+        <v>111</v>
+      </c>
+      <c r="C90" t="str">
+        <v>2X ROUND HEAD</v>
+      </c>
+      <c r="D90" t="str">
+        <v/>
+      </c>
+      <c r="E90" t="str">
+        <v/>
+      </c>
+      <c r="F90" t="str">
+        <v/>
+      </c>
+      <c r="G90" t="str">
+        <v>铅头钩</v>
+      </c>
+      <c r="H90" t="str">
+        <v>pkgGear/images/hook/BKK/2x_round_head.webp</v>
+      </c>
+      <c r="I90" t="str">
+        <v/>
+      </c>
+      <c r="J90" t="str">
+        <v/>
+      </c>
+      <c r="K90" t="str">
+        <v>A modern take on a classic jighead for fresh and saltwater. Black Nickel resists corrosion; 2x‑wire and medium shank ensure strong hooksets while enabling stealthy small‑bait presentations for big predators.</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>BHK1018</v>
+      </c>
+      <c r="B91">
+        <v>111</v>
+      </c>
+      <c r="C91" t="str">
+        <v>Harpax Inshore</v>
+      </c>
+      <c r="D91" t="str">
+        <v/>
+      </c>
+      <c r="E91" t="str">
+        <v/>
+      </c>
+      <c r="F91" t="str">
+        <v/>
+      </c>
+      <c r="G91" t="str">
+        <v>铅头钩</v>
+      </c>
+      <c r="H91" t="str">
+        <v>pkgGear/images/hook/BKK/harpax_inshore.webp</v>
+      </c>
+      <c r="I91" t="str">
+        <v/>
+      </c>
+      <c r="J91" t="str">
+        <v/>
+      </c>
+      <c r="K91" t="str">
+        <v>The BKK Harpax Inshore is a short shank 2x-wire HD jighead equipped with corrosion-resistant Bright-Tin coating developed to be used primarily in saltwater environments. The straight point delivers immediate hook-ups, while the bait keeper is designed to fit most kinds of soft plastic baits including scented, floating or sinking baits whole plastic blend may very significantly. It features an eyelet on the bottom of the head to upgrade it with a teaser blade, an additional treble hook or a stinger.</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>BHK1019</v>
+      </c>
+      <c r="B92">
+        <v>111</v>
+      </c>
+      <c r="C92" t="str">
+        <v>Harpax Offshore</v>
+      </c>
+      <c r="D92" t="str">
+        <v/>
+      </c>
+      <c r="E92" t="str">
+        <v/>
+      </c>
+      <c r="F92" t="str">
+        <v/>
+      </c>
+      <c r="G92" t="str">
+        <v>铅头钩</v>
+      </c>
+      <c r="H92" t="str">
+        <v>pkgGear/images/hook/BKK/harpax_offshore.webp</v>
+      </c>
+      <c r="I92" t="str">
+        <v/>
+      </c>
+      <c r="J92" t="str">
+        <v/>
+      </c>
+      <c r="K92" t="str">
+        <v>The BKK Harpax Offshore is a super heavy-duty jighead designed with a 4x wire and an inward-looking point to be able to withstand extended fights with blue water giants. The design of the bait keeper can accommodate many types of different soft plastic lures.</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>BHK1020</v>
+      </c>
+      <c r="B93">
+        <v>111</v>
+      </c>
+      <c r="C93" t="str">
+        <v>Punch LRF</v>
+      </c>
+      <c r="D93" t="str">
+        <v/>
+      </c>
+      <c r="E93" t="str">
+        <v/>
+      </c>
+      <c r="F93" t="str">
+        <v/>
+      </c>
+      <c r="G93" t="str">
+        <v>铅头钩</v>
+      </c>
+      <c r="H93" t="str">
+        <v>pkgGear/images/hook/BKK/punch_lrf.webp</v>
+      </c>
+      <c r="I93" t="str">
+        <v/>
+      </c>
+      <c r="J93" t="str">
+        <v/>
+      </c>
+      <c r="K93" t="str">
+        <v>Micro Jighead Series is developed to target small fish on light tackle. Specifically designed for rock fishing, it includes three models featuring different head shapes for three different swimming patterns: Harpax Darting LRF, Prisma Darting LRF and Punch LRF. Not only is this series designed to cater to SW inshore rock fishing, but it can find application also in light FW fishing for perch, zander, trout, chub and small carp.</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>BHK1021</v>
+      </c>
+      <c r="B94">
+        <v>111</v>
+      </c>
+      <c r="C94" t="str">
+        <v>Prisma Darting LRF</v>
+      </c>
+      <c r="D94" t="str">
+        <v/>
+      </c>
+      <c r="E94" t="str">
+        <v/>
+      </c>
+      <c r="F94" t="str">
+        <v/>
+      </c>
+      <c r="G94" t="str">
+        <v>铅头钩</v>
+      </c>
+      <c r="H94" t="str">
+        <v>pkgGear/images/hook/BKK/prisma_darting_lrf.webp</v>
+      </c>
+      <c r="I94" t="str">
+        <v/>
+      </c>
+      <c r="J94" t="str">
+        <v/>
+      </c>
+      <c r="K94" t="str">
+        <v>Micro Jighead Series is developed to target small fish on light tackle. Specifically designed for rock fishing, it includes three models featuring different head shapes for three different swimming patterns: Harpax Darting LRF, Prisma Darting LRF and Punch LRF. Not only is this series designed to cater to SW inshore rock fishing, but it can find application also in light FW fishing for perch, zander, trout, chub and small carp. Prisma Darting LRF features an aggressive darting action and performs at its best in weaker current.</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>BHK1022</v>
+      </c>
+      <c r="B95">
+        <v>111</v>
+      </c>
+      <c r="C95" t="str">
+        <v>Harpax Darting LRF</v>
+      </c>
+      <c r="D95" t="str">
+        <v/>
+      </c>
+      <c r="E95" t="str">
+        <v/>
+      </c>
+      <c r="F95" t="str">
+        <v/>
+      </c>
+      <c r="G95" t="str">
+        <v>铅头钩</v>
+      </c>
+      <c r="H95" t="str">
+        <v>pkgGear/images/hook/BKK/harpax_darting_lrf.webp</v>
+      </c>
+      <c r="I95" t="str">
+        <v/>
+      </c>
+      <c r="J95" t="str">
+        <v/>
+      </c>
+      <c r="K95" t="str">
+        <v>Micro Jighead Series is developed to target small fish on light tackle. Specifically designed for rock fishing, it includes three models featuring different head shapes for three different swimming patterns: Harpax Darting LRF, Prisma Darting LRF and Punch LRF. Not only is this series designed to cater to SW inshore rock fishing, but it can find application also in light FW fishing for perch, zander, trout, chub and small carp. Harpax Darting LRF features a moderate darting action and its head shape makes it suitable to be used in heavy current.</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>BHK1023</v>
+      </c>
+      <c r="B96">
+        <v>111</v>
+      </c>
+      <c r="C96" t="str">
+        <v>Draggin’ Ned</v>
+      </c>
+      <c r="D96" t="str">
+        <v/>
+      </c>
+      <c r="E96" t="str">
+        <v/>
+      </c>
+      <c r="F96" t="str">
+        <v/>
+      </c>
+      <c r="G96" t="str">
+        <v>铅头钩</v>
+      </c>
+      <c r="H96" t="str">
+        <v>pkgGear/images/hook/BKK/draggin_ned.webp</v>
+      </c>
+      <c r="I96" t="str">
+        <v/>
+      </c>
+      <c r="J96" t="str">
+        <v/>
+      </c>
+      <c r="K96" t="str">
+        <v>The BKK Draggin’ Ned is designed specifically for Ned Rig presentations. Features include BKK’s signature SS coating and a sharp needle point for enhanced penetration, and an O’Shaughnessy forged bend to maximize strength.</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>BHK1024</v>
+      </c>
+      <c r="B97">
+        <v>111</v>
+      </c>
+      <c r="C97" t="str">
+        <v>Football Head</v>
+      </c>
+      <c r="D97" t="str">
+        <v/>
+      </c>
+      <c r="E97" t="str">
+        <v/>
+      </c>
+      <c r="F97" t="str">
+        <v/>
+      </c>
+      <c r="G97" t="str">
+        <v>铅头钩</v>
+      </c>
+      <c r="H97" t="str">
+        <v>pkgGear/images/hook/BKK/football_head.webp</v>
+      </c>
+      <c r="I97" t="str">
+        <v/>
+      </c>
+      <c r="J97" t="str">
+        <v/>
+      </c>
+      <c r="K97" t="str">
+        <v>The Football-Head is a light jighead featuring a 0.8x-wire and a Cutting Delta point used for finesse presentations with small soft plastic lures on the bottom. The particular shape of the head is designed to jig over stony bottoms avoiding snages, it also slightly changes the swimming action during retrieve and the fluttering action in free sinking compared to a round-head jighead. The hook is coated in Black Nickel to boost your stealthy presentations and to protect the hook.</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>BHK1025</v>
+      </c>
+      <c r="B98">
+        <v>111</v>
+      </c>
+      <c r="C98" t="str">
+        <v>STRAIGHT BAITHOLDER CHEBU</v>
+      </c>
+      <c r="D98" t="str">
+        <v/>
+      </c>
+      <c r="E98" t="str">
+        <v/>
+      </c>
+      <c r="F98" t="str">
+        <v/>
+      </c>
+      <c r="G98" t="str">
+        <v>Swimbait Hooks</v>
+      </c>
+      <c r="H98" t="str">
+        <v>pkgGear/images/hook/BKK/straight_baitholder_chebu.webp</v>
+      </c>
+      <c r="I98" t="str">
+        <v/>
+      </c>
+      <c r="J98" t="str">
+        <v/>
+      </c>
+      <c r="K98" t="str">
+        <v>The Straight Baitholder – Chebu is purpose‑built for use with Cheburashka weights, featuring an oversized eye for free bait movement and a light‑gauge design that keeps presentations stealthy and responsive. Made from Hyper Carbon Steel (HCS) for a strong yet lightweight profile, it sports a Super Slide (SS) finish for effortless penetration and a laser‑welded bait keeper to firmly secure soft plastics, reduce slippage on short strikes and extend bait life—ideal for finesse anglers who demand precise presentation and the durability to land big fish.</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>BHK1026</v>
+      </c>
+      <c r="B99">
+        <v>111</v>
+      </c>
+      <c r="C99" t="str">
+        <v>PERMALOCK-WEIGHTED</v>
+      </c>
+      <c r="D99" t="str">
+        <v/>
+      </c>
+      <c r="E99" t="str">
+        <v/>
+      </c>
+      <c r="F99" t="str">
+        <v/>
+      </c>
+      <c r="G99" t="str">
+        <v>Swimbait Hooks</v>
+      </c>
+      <c r="H99" t="str">
+        <v>pkgGear/images/hook/BKK/permalock_weighted.webp</v>
+      </c>
+      <c r="I99" t="str">
+        <v/>
+      </c>
+      <c r="J99" t="str">
+        <v/>
+      </c>
+      <c r="K99" t="str">
+        <v>The WEIGHTED PERMALOCK is built for finesse presentations and thin‑profile soft plastics like Senkos and flukes. Its INVISI‑WEIGHT system gives the bait a natural, stealthy glide and keeps a horizontal posture in the water column—perfect for FFS fishing near structure. Made from Hyper Carbon Steel (HCS) with a Super Slide (SS) finish and an extra‑sharp needle point, it delivers strong penetration and improved hook‑up rates.</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>BHK1027</v>
+      </c>
+      <c r="B100">
+        <v>111</v>
+      </c>
+      <c r="C100" t="str">
+        <v>PERMALOCK-HD</v>
+      </c>
+      <c r="D100" t="str">
+        <v/>
+      </c>
+      <c r="E100" t="str">
+        <v/>
+      </c>
+      <c r="F100" t="str">
+        <v/>
+      </c>
+      <c r="G100" t="str">
+        <v>Swimbait Hooks</v>
+      </c>
+      <c r="H100" t="str">
+        <v>pkgGear/images/hook/BKK/permalock_hd.webp</v>
+      </c>
+      <c r="I100" t="str">
+        <v/>
+      </c>
+      <c r="J100" t="str">
+        <v/>
+      </c>
+      <c r="K100" t="str">
+        <v>The PERMALOCK‑HD is a heavy‑duty Permalock hook engineered for trophy‑sized fish and high‑drag situations. Versatile for swimbaits, senkos, flukes, toads and craws, it promotes more effective hooksets. Made from Hyper Carbon Steel (HCS) and finished with Super Slide (SS) plus an extra‑sharp needle point, it delivers exceptional penetration, improved hook‑up rates and long‑lasting strength.</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>BHK1028</v>
+      </c>
+      <c r="B101">
+        <v>111</v>
+      </c>
+      <c r="C101" t="str">
+        <v>PERMALOCK TUNGSTEN NAIL KEEPER</v>
+      </c>
+      <c r="D101" t="str">
+        <v/>
+      </c>
+      <c r="E101" t="str">
+        <v/>
+      </c>
+      <c r="F101" t="str">
+        <v/>
+      </c>
+      <c r="G101" t="str">
+        <v>Swimbait Hooks</v>
+      </c>
+      <c r="H101" t="str">
+        <v>pkgGear/images/hook/BKK/permalock_tungsten_nail_keeper.webp</v>
+      </c>
+      <c r="I101" t="str">
+        <v/>
+      </c>
+      <c r="J101" t="str">
+        <v/>
+      </c>
+      <c r="K101" t="str">
+        <v>The PERMALOCK‑HD is an extra‑robust Permalock hook built to handle trophy‑sized fish and heavy drag settings. Ideal for a wide range of soft plastics—swimbaits, senkos, flukes, toads and craws—it delivers more secure hooksets. Made from Hyper Carbon Steel (HCS) and finished with BKK’s Super Slide (SS) coating plus an extra‑sharp needle point, it provides exceptional penetration, higher hook‑up rates and outstanding durability.</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>BHK1029</v>
+      </c>
+      <c r="B102">
+        <v>111</v>
+      </c>
+      <c r="C102" t="str">
+        <v>PERMALOCK</v>
+      </c>
+      <c r="D102" t="str">
+        <v/>
+      </c>
+      <c r="E102" t="str">
+        <v/>
+      </c>
+      <c r="F102" t="str">
+        <v/>
+      </c>
+      <c r="G102" t="str">
+        <v>Swimbait Hooks</v>
+      </c>
+      <c r="H102" t="str">
+        <v>pkgGear/images/hook/BKK/permalock.webp</v>
+      </c>
+      <c r="I102" t="str">
+        <v/>
+      </c>
+      <c r="J102" t="str">
+        <v/>
+      </c>
+      <c r="K102" t="str">
+        <v>The PERMALOCK is tailored for finesse presentations and thin‑profile soft plastics such as senkos and flukes. Constructed from Hyper Carbon Steel (HCS) and finished with Super Slide (SS) plus an extra‑sharp needle point, it delivers excellent penetration and improved hook‑up rates while providing the strength and reliability anglers depend on.</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>BHK1030</v>
+      </c>
+      <c r="B103">
+        <v>111</v>
+      </c>
+      <c r="C103" t="str">
+        <v>OFFSET WORM WG-HD</v>
+      </c>
+      <c r="D103" t="str">
+        <v/>
+      </c>
+      <c r="E103" t="str">
+        <v/>
+      </c>
+      <c r="F103" t="str">
+        <v/>
+      </c>
+      <c r="G103" t="str">
+        <v>Swimbait Hooks</v>
+      </c>
+      <c r="H103" t="str">
+        <v>pkgGear/images/hook/BKK/offset_worm_wg_hd.webp</v>
+      </c>
+      <c r="I103" t="str">
+        <v/>
+      </c>
+      <c r="J103" t="str">
+        <v/>
+      </c>
+      <c r="K103" t="str">
+        <v>heavy‑diameter, wide‑gap Texas hook for big bass and heavy cover with sealed eye and HCS strength.</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>BHK1031</v>
+      </c>
+      <c r="B104">
+        <v>111</v>
+      </c>
+      <c r="C104" t="str">
+        <v>OFFSET WORM WG</v>
+      </c>
+      <c r="D104" t="str">
+        <v/>
+      </c>
+      <c r="E104" t="str">
+        <v/>
+      </c>
+      <c r="F104" t="str">
+        <v/>
+      </c>
+      <c r="G104" t="str">
+        <v>Swimbait Hooks</v>
+      </c>
+      <c r="H104" t="str">
+        <v>pkgGear/images/hook/BKK/offset_worm_wg.webp</v>
+      </c>
+      <c r="I104" t="str">
+        <v/>
+      </c>
+      <c r="J104" t="str">
+        <v/>
+      </c>
+      <c r="K104" t="str">
+        <v>The OFFSET WORM WG features a wide gap and enhanced Z‑bend for quick, secure Texas rigging of senkos, shads, flukes and creature baits. Built from Hyper Carbon Steel (HCS) with a Super Slide (SS) finish and an extra‑sharp needle point, it offers excellent penetration, higher hook‑up rates and improved plastic retention with reduced bait damage.</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>BHK1032</v>
+      </c>
+      <c r="B105">
+        <v>111</v>
+      </c>
+      <c r="C105" t="str">
+        <v>OFFSET WORM ROUND BEND</v>
+      </c>
+      <c r="D105" t="str">
+        <v/>
+      </c>
+      <c r="E105" t="str">
+        <v/>
+      </c>
+      <c r="F105" t="str">
+        <v/>
+      </c>
+      <c r="G105" t="str">
+        <v>Swimbait Hooks</v>
+      </c>
+      <c r="H105" t="str">
+        <v>pkgGear/images/hook/BKK/offset_worm_round_bend.webp</v>
+      </c>
+      <c r="I105" t="str">
+        <v/>
+      </c>
+      <c r="J105" t="str">
+        <v/>
+      </c>
+      <c r="K105" t="str">
+        <v>The OFFSET WORM ROUND BEND is designed for Texas‑rigging a wide range of plastic worms. Constructed from Hyper Carbon Steel (HCS) and finished with Super Slide (SS) plus an extra‑sharp needle point, it delivers excellent penetration and improved hook‑up rates while offering enhanced strength and reliability.</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>BHK1033</v>
+      </c>
+      <c r="B106">
+        <v>111</v>
+      </c>
+      <c r="C106" t="str">
+        <v>OFFSET WORM EWG CHEBU</v>
+      </c>
+      <c r="D106" t="str">
+        <v/>
+      </c>
+      <c r="E106" t="str">
+        <v/>
+      </c>
+      <c r="F106" t="str">
+        <v/>
+      </c>
+      <c r="G106" t="str">
+        <v>Swimbait Hooks</v>
+      </c>
+      <c r="H106" t="str">
+        <v>pkgGear/images/hook/BKK/offset_worm_ewg_chebu.webp</v>
+      </c>
+      <c r="I106" t="str">
+        <v/>
+      </c>
+      <c r="J106" t="str">
+        <v/>
+      </c>
+      <c r="K106" t="str">
+        <v>The Armorpoint Offset Worm EWG-Chebu is engineered for Cheburashka setups, featuring an oversized eye that lets the bait pivot freely for a natural, dynamic presentation. Its extra‑wide gap accommodates bulky soft plastics and exposes the point for reliable penetration. Made from Hyper Carbon Steel (HCS) for superior tensile strength, and finished with Super Slide (SS) plus a needle‑sharp point, it delivers effortless penetration and dependable hook‑up performance in heavy cover.</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>BHK1034</v>
+      </c>
+      <c r="B107">
+        <v>111</v>
+      </c>
+      <c r="C107" t="str">
+        <v>OFFSET WORM EWG</v>
+      </c>
+      <c r="D107" t="str">
+        <v/>
+      </c>
+      <c r="E107" t="str">
+        <v/>
+      </c>
+      <c r="F107" t="str">
+        <v/>
+      </c>
+      <c r="G107" t="str">
+        <v>Swimbait Hooks</v>
+      </c>
+      <c r="H107" t="str">
+        <v>pkgGear/images/hook/BKK/offset_worm_ewg.webp</v>
+      </c>
+      <c r="I107" t="str">
+        <v/>
+      </c>
+      <c r="J107" t="str">
+        <v/>
+      </c>
+      <c r="K107" t="str">
+        <v>The OFFSET WORM EWG is designed for Texas‑rigging larger soft plastics—creature baits, shads, and oversized worms—offering an extra‑wide gap that lets the lure collapse and exposes the point for deeper penetration. Built from Hyper Carbon Steel (HCS) with a Super Slide (SS) finish and an extra‑sharp needle point, it delivers effortless hook penetration, higher hook‑up rates, and exceptional durability.</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>BHK1035</v>
+      </c>
+      <c r="B108">
+        <v>111</v>
+      </c>
+      <c r="C108" t="str">
+        <v>MOTHER FLUKER</v>
+      </c>
+      <c r="D108" t="str">
+        <v/>
+      </c>
+      <c r="E108" t="str">
+        <v/>
+      </c>
+      <c r="F108" t="str">
+        <v/>
+      </c>
+      <c r="G108" t="str">
+        <v>Swimbait Hooks</v>
+      </c>
+      <c r="H108" t="str">
+        <v>pkgGear/images/hook/BKK/mother_fluker.webp</v>
+      </c>
+      <c r="I108" t="str">
+        <v/>
+      </c>
+      <c r="J108" t="str">
+        <v/>
+      </c>
+      <c r="K108" t="str">
+        <v>The MOTHERFLUKER is a baitholder‑style hook engineered for soft plastics, built from Hyper Carbon Steel (HCS) for added strength and durability when targeting trophy fish. Laser‑welded baitholder barbs lock baits in place through short strikes, while an ultra‑sharp needle point paired with BKK’s Super Slide (SS) coating enables faster, deeper penetration and improved hook‑up performance.</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>BHK1036</v>
+      </c>
+      <c r="B109">
+        <v>111</v>
+      </c>
+      <c r="C109" t="str">
+        <v>HEAVY COVER-FLIPPING HOOK</v>
+      </c>
+      <c r="D109" t="str">
+        <v/>
+      </c>
+      <c r="E109" t="str">
+        <v/>
+      </c>
+      <c r="F109" t="str">
+        <v/>
+      </c>
+      <c r="G109" t="str">
+        <v>Swimbait Hooks</v>
+      </c>
+      <c r="H109" t="str">
+        <v>pkgGear/images/hook/BKK/heavy_cover_flipping_hook.webp</v>
+      </c>
+      <c r="I109" t="str">
+        <v/>
+      </c>
+      <c r="J109" t="str">
+        <v/>
+      </c>
+      <c r="K109" t="str">
+        <v>The HEAVY COVER is purpose‑built for flipping and punching, featuring Hyper Carbon Steel (HCS) wire for superior strength and a Super Slide (SS) finish with an extra‑short needle point for exceptional penetration and point durability. A stainless‑steel bait keeper ensures straight, secure rigging, while epoxy‑sealed eyes protect line and enable reliable snell knots with braided lines.</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>BHK1037</v>
+      </c>
+      <c r="B110">
+        <v>111</v>
+      </c>
+      <c r="C110" t="str">
+        <v>DROPSHOT-LONG SHANK</v>
+      </c>
+      <c r="D110" t="str">
+        <v/>
+      </c>
+      <c r="E110" t="str">
+        <v/>
+      </c>
+      <c r="F110" t="str">
+        <v/>
+      </c>
+      <c r="G110" t="str">
+        <v>Swimbait Hooks</v>
+      </c>
+      <c r="H110" t="str">
+        <v>pkgGear/images/hook/BKK/dropshot_long_shank.webp</v>
+      </c>
+      <c r="I110" t="str">
+        <v/>
+      </c>
+      <c r="J110" t="str">
+        <v/>
+      </c>
+      <c r="K110" t="str">
+        <v>The LONG SHANK DROPSHOT is crafted for finesse presentations and soft‑plastic worm rigging; its bait keeper on the shank ensures consistently straight rigs and superior holding power. Made from stronger Hyper Carbon Steel (HCS) and finished with Super Slide (SS) plus an extra‑sharp needle point, it delivers reliable penetration and boosted hook‑up rates.</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>BHK1038</v>
+      </c>
+      <c r="B111">
+        <v>111</v>
+      </c>
+      <c r="C111" t="str">
+        <v>DROPSHOT</v>
+      </c>
+      <c r="D111" t="str">
+        <v/>
+      </c>
+      <c r="E111" t="str">
+        <v/>
+      </c>
+      <c r="F111" t="str">
+        <v/>
+      </c>
+      <c r="G111" t="str">
+        <v>Swimbait Hooks</v>
+      </c>
+      <c r="H111" t="str">
+        <v>pkgGear/images/hook/BKK/dropshot.webp</v>
+      </c>
+      <c r="I111" t="str">
+        <v/>
+      </c>
+      <c r="J111" t="str">
+        <v/>
+      </c>
+      <c r="K111" t="str">
+        <v>The DROPSHOT is built for drop shotting and light‑tackle use, positioning nose‑hooked worms to maximize tail action and hold an ideal hook setting when fishing vertically. Made from stronger Hyper Carbon Steel (HCS) and finished with Super Slide (SS) plus an extra‑sharp needle point, it delivers reliable penetration and improved hook‑up rates.</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>BHK1039</v>
+      </c>
+      <c r="B112">
+        <v>111</v>
+      </c>
+      <c r="C112" t="str">
+        <v>DOUBLE-61 SS</v>
+      </c>
+      <c r="D112" t="str">
+        <v/>
+      </c>
+      <c r="E112" t="str">
+        <v/>
+      </c>
+      <c r="F112" t="str">
+        <v/>
+      </c>
+      <c r="G112" t="str">
+        <v>Swimbait Hooks</v>
+      </c>
+      <c r="H112" t="str">
+        <v>pkgGear/images/hook/BKK/double_61_ss.webp</v>
+      </c>
+      <c r="I112" t="str">
+        <v/>
+      </c>
+      <c r="J112" t="str">
+        <v/>
+      </c>
+      <c r="K112" t="str">
+        <v>The Double‑61 SS is a medium‑wire, long‑shank double hook engineered for silicone lure rigging. Its extended shank sets the points about one‑third down the bait to boost hook‑up ratios while preserving bait action. Finished with Super Slide coating and an extra‑sharp needle point for fast, reliable penetration and improved landing rates.</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>BHK1040</v>
+      </c>
+      <c r="B113">
+        <v>111</v>
+      </c>
+      <c r="C113" t="str">
+        <v>Titandiver Gold</v>
+      </c>
+      <c r="D113" t="str">
+        <v/>
+      </c>
+      <c r="E113" t="str">
+        <v/>
+      </c>
+      <c r="F113" t="str">
+        <v/>
+      </c>
+      <c r="G113" t="str">
+        <v>Swimbait Hooks</v>
+      </c>
+      <c r="H113" t="str">
+        <v>pkgGear/images/hook/BKK/titandiver_gold.webp</v>
+      </c>
+      <c r="I113" t="str">
+        <v/>
+      </c>
+      <c r="J113" t="str">
+        <v/>
+      </c>
+      <c r="K113" t="str">
+        <v>The BKK Titandiver gold is a new and upgraded version of the Titanrider, designed for weedless-style rigging of soft plastics. It maintains all the features of the original Titanrider, including a locking spring to secure the bait, a silicone stopper to keep it in place, and the Super Slide coating. In addition, it features a fixed weight that aids in presenting the lure down into the strike zone.</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>BHK1041</v>
+      </c>
+      <c r="B114">
+        <v>111</v>
+      </c>
+      <c r="C114" t="str">
+        <v>Titan Rider</v>
+      </c>
+      <c r="D114" t="str">
+        <v/>
+      </c>
+      <c r="E114" t="str">
+        <v/>
+      </c>
+      <c r="F114" t="str">
+        <v/>
+      </c>
+      <c r="G114" t="str">
+        <v>Swimbait Hooks</v>
+      </c>
+      <c r="H114" t="str">
+        <v>pkgGear/images/hook/BKK/titan_rider.webp</v>
+      </c>
+      <c r="I114" t="str">
+        <v/>
+      </c>
+      <c r="J114" t="str">
+        <v/>
+      </c>
+      <c r="K114" t="str">
+        <v>The Titan Rider is designed for weedless-style rigging of large soft plastic baits such as big swimbaits and tubes. With more than a year of field tests with different species underlie the construction quality and the versatility of the hook. The hook is equipped with a locking spring that securely holds baits in place and allows anglers to easily add or remove soft baits.</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>BHK1042</v>
+      </c>
+      <c r="B115">
+        <v>111</v>
+      </c>
+      <c r="C115" t="str">
+        <v>Titan Diver+</v>
+      </c>
+      <c r="D115" t="str">
+        <v/>
+      </c>
+      <c r="E115" t="str">
+        <v/>
+      </c>
+      <c r="F115" t="str">
+        <v/>
+      </c>
+      <c r="G115" t="str">
+        <v>Swimbait Hooks</v>
+      </c>
+      <c r="H115" t="str">
+        <v>pkgGear/images/hook/BKK/titan_diver.webp</v>
+      </c>
+      <c r="I115" t="str">
+        <v/>
+      </c>
+      <c r="J115" t="str">
+        <v/>
+      </c>
+      <c r="K115" t="str">
+        <v>The BKK Titan Diver+ is the ultimate evolution of the Titan series. Potentially a breakthrough in the worm hook segments, the Diver+ inherits all the features of an ordinary Titan hook – Super Slide coating, needle point, spring and silicon stopper - enhanced with a simple, intuitive and effective lead-swapping system.</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>BHK1043</v>
+      </c>
+      <c r="B116">
+        <v>111</v>
+      </c>
+      <c r="C116" t="str">
+        <v>Titan Diver</v>
+      </c>
+      <c r="D116" t="str">
+        <v/>
+      </c>
+      <c r="E116" t="str">
+        <v/>
+      </c>
+      <c r="F116" t="str">
+        <v/>
+      </c>
+      <c r="G116" t="str">
+        <v>Swimbait Hooks</v>
+      </c>
+      <c r="H116" t="str">
+        <v>pkgGear/images/hook/BKK/titan_diver.webp</v>
+      </c>
+      <c r="I116" t="str">
+        <v/>
+      </c>
+      <c r="J116" t="str">
+        <v/>
+      </c>
+      <c r="K116" t="str">
+        <v>The BKK Titan Diver is the new, upgraded version of the Titan, designed for weedless-style rigging of larger plastics. It features all the characteristics of the original Titan – a locking spring to secure the plastic lure, a silicone stopper to keep it in place and the Super Slide coating – boosted by the addition of a fixed lead to take the fishing action deeper in the water, scouting sunken structures where predator fish may dwell. The lead in turn features a stainless-steel ring to allow for the attachment of a spinning blade, improving the appeal of your lure.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K72"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K116"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/GearSage-client/rate/excel/hook.xlsx
+++ b/GearSage-client/rate/excel/hook.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K116"/>
+  <dimension ref="A1:K141"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4459,9 +4459,884 @@
         <v>The BKK Titan Diver is the new, upgraded version of the Titan, designed for weedless-style rigging of larger plastics. It features all the characteristics of the original Titan – a locking spring to secure the plastic lure, a silicone stopper to keep it in place and the Super Slide coating – boosted by the addition of a fixed lead to take the fishing action deeper in the water, scouting sunken structures where predator fish may dwell. The lead in turn features a stainless-steel ring to allow for the attachment of a spinning blade, improving the appeal of your lure.</v>
       </c>
     </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>MHK1000</v>
+      </c>
+      <c r="B117">
+        <v>112</v>
+      </c>
+      <c r="C117" t="str">
+        <v>Grip-Pin® Big Bite™ Soft Plastics Hook</v>
+      </c>
+      <c r="D117" t="str">
+        <v/>
+      </c>
+      <c r="E117" t="str">
+        <v/>
+      </c>
+      <c r="F117" t="str">
+        <v/>
+      </c>
+      <c r="G117" t="str">
+        <v>曲柄钩 / Offset / Wide Gap</v>
+      </c>
+      <c r="H117" t="str">
+        <v>pkgGear/images/hook/MUSTAD/grip_pin_big_bite_soft_plastics_hook.jpg</v>
+      </c>
+      <c r="I117" t="str">
+        <v/>
+      </c>
+      <c r="J117" t="str">
+        <v/>
+      </c>
+      <c r="K117" t="str">
+        <v>The Mustad Grip-Pin® hooks feature a molded resin pin that securely anchors a wide range of baits to the hook for a "no slip, no slide" design without tearing the soft bait. The 2X long shank hook is ideal choice for a wide range of large soft plastic lures such as shads, worms or swim baits. The 2X strong wire hook is perfect fishing around heavy cover targeting a wide variety of species, such as big Bass, Perch, Brown Trout, Rainbow Trout, Zander, Pike or Walleye. Coated with Mustad's own Black Nickel finish, which is 4 times as rust resistant as traditional Black Nickel. 4.3 UltraPoint® Technology Opti-Angle Needle Point 2X Strong 2X Long shank Straight shank Ringed eye Forged Nor-Tempered</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>MHK1001</v>
+      </c>
+      <c r="B118">
+        <v>112</v>
+      </c>
+      <c r="C118" t="str">
+        <v>Select Finesse Hook - 1X Fine</v>
+      </c>
+      <c r="D118" t="str">
+        <v/>
+      </c>
+      <c r="E118" t="str">
+        <v/>
+      </c>
+      <c r="F118" t="str">
+        <v/>
+      </c>
+      <c r="G118" t="str">
+        <v>倒钓钩 / Drop Shot</v>
+      </c>
+      <c r="H118" t="str">
+        <v>pkgGear/images/hook/MUSTAD/select_finesse_hook_1x_fine.jpg</v>
+      </c>
+      <c r="I118" t="str">
+        <v/>
+      </c>
+      <c r="J118" t="str">
+        <v/>
+      </c>
+      <c r="K118" t="str">
+        <v>This 1X fine wire hook for a delicate drop shot presentation when you nose hook the bait or as attached to tiny lures. Round bend wide gape for great hooking ability and presentation. Up-turned eye makes it perfect for the Snell knot and suspended presentation. This is truly a must-have hook for freshwater anglers, who expect the best from a hook. 4.3 UltraPoint® Technology Opti-Angle Needle Point 1X Fine Wire Ringed eye Nor-Tempered</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>MHK1002</v>
+      </c>
+      <c r="B119">
+        <v>112</v>
+      </c>
+      <c r="C119" t="str">
+        <v>KVD Grip-Pin® Soft Plastics Hook</v>
+      </c>
+      <c r="D119" t="str">
+        <v/>
+      </c>
+      <c r="E119" t="str">
+        <v/>
+      </c>
+      <c r="F119" t="str">
+        <v/>
+      </c>
+      <c r="G119" t="str">
+        <v>曲柄钩 / Offset / Wide Gap</v>
+      </c>
+      <c r="H119" t="str">
+        <v>pkgGear/images/hook/MUSTAD/kvd_grip_pin_soft_plastics_hook.jpg</v>
+      </c>
+      <c r="I119" t="str">
+        <v/>
+      </c>
+      <c r="J119" t="str">
+        <v/>
+      </c>
+      <c r="K119" t="str">
+        <v>The Grip-Pin® Soft Plastic fish hooks feature a molded resin pin that securely anchors a wide range of baits to the hook for a "no slip, no slide" design without tearing the bait. This extra wide bend bass fishing hook is ideal choice for a wide range of soft plastic lures such as shads, worms or swim baits. The 1X strong wire makes a great platform for fishing near hard cover and vegetation. Our Grip-Pinss are the best hooks for fishing Bass, Perch, Brown Trout, Rainbow Trout, Zander, Pike or Walleye. Coated with Mustad's own Black Nickel finish, which are 4 times as corrosion resistant as traditional Black Nickel. 4.3 UltraPoint® Technology Opti-Angle Needle Point 1X Strong Extra wide bend Ringed Eye Nor-Tempered Resin-coated Grip Pin® Black Nickel finish</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>MHK1003</v>
+      </c>
+      <c r="B120">
+        <v>112</v>
+      </c>
+      <c r="C120" t="str">
+        <v>Grip-Pin Edge® Finesse Soft Plastics Hook</v>
+      </c>
+      <c r="D120" t="str">
+        <v/>
+      </c>
+      <c r="E120" t="str">
+        <v/>
+      </c>
+      <c r="F120" t="str">
+        <v/>
+      </c>
+      <c r="G120" t="str">
+        <v>倒钓钩 / Drop Shot</v>
+      </c>
+      <c r="H120" t="str">
+        <v>pkgGear/images/hook/MUSTAD/grip_pin_edge_finesse_soft_plastics_hook.jpg</v>
+      </c>
+      <c r="I120" t="str">
+        <v/>
+      </c>
+      <c r="J120" t="str">
+        <v/>
+      </c>
+      <c r="K120" t="str">
+        <v>The Mustad Grip-Pin® Edge Finesse Hook is designed for soft plastic swim baits, especially worms. It features a molded resin pin that securely anchors the front end of the soft plastic lure with a "no slip, no slide" design, without tearing the bait. It is ideal for fishing weedless with perfect presentation and hooking properties. Fish it weightless or Texas or Drop Shot style to get at the deeper swimming fish. Use it for Bass, Perch, Zander, Brown Trout, Rainbow Trout, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point Straight Long shank Ringed eye Nor-Tempered PVC coated Grip Pin® Black Nickel finish</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>MHK1004</v>
+      </c>
+      <c r="B121">
+        <v>112</v>
+      </c>
+      <c r="C121" t="str">
+        <v>Double Wide Gap Dropshot Hook</v>
+      </c>
+      <c r="D121" t="str">
+        <v/>
+      </c>
+      <c r="E121" t="str">
+        <v/>
+      </c>
+      <c r="F121" t="str">
+        <v/>
+      </c>
+      <c r="G121" t="str">
+        <v>曲柄钩 / Offset / Wide Gap</v>
+      </c>
+      <c r="H121" t="str">
+        <v>pkgGear/images/hook/MUSTAD/double_wide_gap_dropshot_hook.png</v>
+      </c>
+      <c r="I121" t="str">
+        <v/>
+      </c>
+      <c r="J121" t="str">
+        <v/>
+      </c>
+      <c r="K121" t="str">
+        <v>A dropshot rig is an efficient method for positioning your soft plastic lure near the bottom while avoiding snags. This wide gap Dropshot Hook ensures a gentle presentation of your bait, maximizing its appeal to fish while offering a wider gape that anglers find effective in many applications. Experiment with suspended or bouncing motions, incorporating spin stops for added allure. Secure your hook with the reliable Palomar knot, ensuring a precise 90-degree angle from the line. Target species like Bass, Perch, or Trout with this hook. 4.3 UltraPoint® Technology Opti-Angle Needle Point Wide Gap Forged Ringed eye Up Eye Nor-Tempered</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>MHK1005</v>
+      </c>
+      <c r="B122">
+        <v>112</v>
+      </c>
+      <c r="C122" t="str">
+        <v>Dropshot Hook</v>
+      </c>
+      <c r="D122" t="str">
+        <v/>
+      </c>
+      <c r="E122" t="str">
+        <v/>
+      </c>
+      <c r="F122" t="str">
+        <v/>
+      </c>
+      <c r="G122" t="str">
+        <v>倒钓钩 / Drop Shot</v>
+      </c>
+      <c r="H122" t="str">
+        <v>pkgGear/images/hook/MUSTAD/dropshot_hook.jpg</v>
+      </c>
+      <c r="I122" t="str">
+        <v/>
+      </c>
+      <c r="J122" t="str">
+        <v/>
+      </c>
+      <c r="K122" t="str">
+        <v>Fishing the drop shot rig is an effective way to present your soft plastic lure close to the bottom, without snagging. The fine wire hook offers a delicate presentation of your lure. Fish it with a suspended presentation with a steady motion, or let it bounce off the bottom, leaving as many spin stops you like. Your soft plastic lure will be right in the striking zone. The best knot for tying the hook to the line is the Palomar knot, which will place it at a 90-degree angle from the line. Use it to target Bass, Perch or Trout in rivers, lakes or canals. 4.3 UltraPoint® Technology Opti-Angle Needle Point Ringed eye Up eye Nor-Tempered</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>MHK1006</v>
+      </c>
+      <c r="B123">
+        <v>112</v>
+      </c>
+      <c r="C123" t="str">
+        <v>TitanX Wacky / Neko / Dropshot Hook</v>
+      </c>
+      <c r="D123" t="str">
+        <v/>
+      </c>
+      <c r="E123" t="str">
+        <v/>
+      </c>
+      <c r="F123" t="str">
+        <v/>
+      </c>
+      <c r="G123" t="str">
+        <v>倒钓钩 / Drop Shot</v>
+      </c>
+      <c r="H123" t="str">
+        <v>pkgGear/images/hook/MUSTAD/titanx_wacky_neko_dropshot_hook.jpg</v>
+      </c>
+      <c r="I123" t="str">
+        <v/>
+      </c>
+      <c r="J123" t="str">
+        <v/>
+      </c>
+      <c r="K123" t="str">
+        <v>The TitanX Wacky/Neko Hook features a non-reflective, natural look that won't spook the fish in clear conditions, but provide 4 times better penetration as well. Made for multiple techniques such as Wacky, Neko or Drop shot rigging. “They are the best drop shot/wacky rig hooks I have ever used” - says Mustad Pro Staff Kevin VanDam - and he has the tournament wins to prove it. Perfect for using with a great variety of soft plastic worms, targeting deeper lying fish around structures, drop-offs or ledges. This technique has a great variety of applications in both fresh and saltwater, targeting Largemouth or Smallmouth Bass, Northern Pike, Muskie, Perch, Zander, Walleye, Brown Trout, Redfish, Speckled Sea Trout, Snook, Redfish, Striped Bass, Cod or Dorado/Mahi Mahi. The TitanX Wacky/Neko hook has also become popular among saltwater fly fishermen when tying crab imitations targeting Redfish, Bonefish, Black Drum and Sea Trout. 4.3 UltraPoint® Technology Opti-Angle Needle Point 2X Long Sproat bend Wide Gap Ringed eye TitanX finish</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>MHK1007</v>
+      </c>
+      <c r="B124">
+        <v>112</v>
+      </c>
+      <c r="C124" t="str">
+        <v>Mega Bite® Soft Plastics Hook</v>
+      </c>
+      <c r="D124" t="str">
+        <v/>
+      </c>
+      <c r="E124" t="str">
+        <v/>
+      </c>
+      <c r="F124" t="str">
+        <v/>
+      </c>
+      <c r="G124" t="str">
+        <v>曲柄钩 / Offset / Wide Gap</v>
+      </c>
+      <c r="H124" t="str">
+        <v>pkgGear/images/hook/MUSTAD/mega_bite_soft_plastics_hook.jpg</v>
+      </c>
+      <c r="I124" t="str">
+        <v/>
+      </c>
+      <c r="J124" t="str">
+        <v/>
+      </c>
+      <c r="K124" t="str">
+        <v>The Mega Bite® Worm Offset Shank fish Hook is designed for soft large plastic worms. It is a perfect setup for free water fishing with the hook exposed. The wide gap and extra wide bend leaves room for more bulky soft plastic worms. Fish it Texas or Carolina rig style or just free swimming. Use it for Bass, Perch, Zander, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point Extra wide bend Ringed eye Nor-Tempered</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>MHK1008</v>
+      </c>
+      <c r="B125">
+        <v>112</v>
+      </c>
+      <c r="C125" t="str">
+        <v>Big Mouth Tube Hook</v>
+      </c>
+      <c r="D125" t="str">
+        <v/>
+      </c>
+      <c r="E125" t="str">
+        <v/>
+      </c>
+      <c r="F125" t="str">
+        <v/>
+      </c>
+      <c r="G125" t="str">
+        <v>曲柄钩 / Offset / Wide Gap</v>
+      </c>
+      <c r="H125" t="str">
+        <v>pkgGear/images/hook/MUSTAD/big_mouth_tube_hook.jpg</v>
+      </c>
+      <c r="I125" t="str">
+        <v/>
+      </c>
+      <c r="J125" t="str">
+        <v/>
+      </c>
+      <c r="K125" t="str">
+        <v>Crush big freshwater predators with Mustad's Big Mouth hooks paired with your favorite large soft plastic worms. Bulky baits present perfectly thanks to the wide gap and extra wide bend. Anglers often fish this freely with the hook exposed, or in Texas or Carolina rigs. Use it for Bass, Perch, Zander, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point Extra wide bend Offset shank 1X Strong Ringed eye Nor-Tempered</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>MHK1009</v>
+      </c>
+      <c r="B126">
+        <v>112</v>
+      </c>
+      <c r="C126" t="str">
+        <v>Weighted KVD Grip Pin® Hook</v>
+      </c>
+      <c r="D126" t="str">
+        <v/>
+      </c>
+      <c r="E126" t="str">
+        <v/>
+      </c>
+      <c r="F126" t="str">
+        <v/>
+      </c>
+      <c r="G126" t="str">
+        <v>曲柄钩 / Offset / Wide Gap</v>
+      </c>
+      <c r="H126" t="str">
+        <v>pkgGear/images/hook/MUSTAD/weighted_kvd_grip_pin_hook.jpg</v>
+      </c>
+      <c r="I126" t="str">
+        <v/>
+      </c>
+      <c r="J126" t="str">
+        <v/>
+      </c>
+      <c r="K126" t="str">
+        <v>The Weighted Grip Pin® Hook features a molded resin pin that securely anchors a wide range of baits to the hook for a "no slip, no slide" design without tearing the bait. Expanding upon Mustad’s popular Grip-Pin series, the Mustad Weighted KVD Grip Pin Hook features a sleek integrated 1/8oz/3,54g perfectly balanced belly weight, which allows anglers to effectively fish deeper waters. The 1X strong wire makes a great platform for fishing near hard cover and vegetation. The hook is designed for a big range of soft plastic lures such as shads, worms or swim baits. Use it to catch Bass, Perch, Zander, Brown Trout, Rainbow Trout, Pike or Walleye. Coated with Mustad's own Black Nickel finish, which is 4 times as rust resistant as traditional Black Nickel. 4.3 UltraPoint® Technology Opti-Angle Needle Point 1X Strong Extra wide bend Ringed eye Forged Nor-Tempered 1/8oz/3,54g weighted hook Resin-coated Grip Pin® Black Nickel finish</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>MHK1010</v>
+      </c>
+      <c r="B127">
+        <v>112</v>
+      </c>
+      <c r="C127" t="str">
+        <v>Power Lock Plus Spring Keeper Hook - Weighted</v>
+      </c>
+      <c r="D127" t="str">
+        <v/>
+      </c>
+      <c r="E127" t="str">
+        <v/>
+      </c>
+      <c r="F127" t="str">
+        <v/>
+      </c>
+      <c r="G127" t="str">
+        <v>特种钩 / Swimbait Hook</v>
+      </c>
+      <c r="H127" t="str">
+        <v>pkgGear/images/hook/MUSTAD/power_lock_plus_spring_keeper_hook_weighted.png</v>
+      </c>
+      <c r="I127" t="str">
+        <v/>
+      </c>
+      <c r="J127" t="str">
+        <v/>
+      </c>
+      <c r="K127" t="str">
+        <v>The Power Lock Plus Spring Keeper Hook features a tapered spring gripper, offering a secure hold for your favorite swimbait with as much as 80% more grip strength. The unique adjustable sliding, build-in weight allows for back, forward or centered presentation. Moving the weight is easy. Rotate the weight several times to heat silicon insert. Move weight to desired position. As the insert cools, the weight will be held firmly in place again. Back position will push the bait backwards under structures like logs and docks. Use with tube baits, crawfish or jerkbaits. Forward position will make the bait dive nose down. Centered position will make the bait sink horizontally. The wide gap provides excellent hooking and holding abilities for big fish. Use it for Bass, Perch, Zander, Pike or Walleye.</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>MHK1011</v>
+      </c>
+      <c r="B128">
+        <v>112</v>
+      </c>
+      <c r="C128" t="str">
+        <v>KVD Weedless Wacky Worm Hook</v>
+      </c>
+      <c r="D128" t="str">
+        <v/>
+      </c>
+      <c r="E128" t="str">
+        <v/>
+      </c>
+      <c r="F128" t="str">
+        <v/>
+      </c>
+      <c r="G128" t="str">
+        <v>倒钓钩 / Wacky</v>
+      </c>
+      <c r="H128" t="str">
+        <v>pkgGear/images/hook/MUSTAD/kvd_weedless_wacky_worm_hook.jpg</v>
+      </c>
+      <c r="I128" t="str">
+        <v/>
+      </c>
+      <c r="J128" t="str">
+        <v/>
+      </c>
+      <c r="K128" t="str">
+        <v>The Mustad KVD Wacky Worm Hook is the perfect wide gap heavy cover hook targeting everything from big Bass and Redfish along with many other strong saltwater species. Perfect for tube bait soft lures. Fish it Wacky or Dropshot style. Rigging the tube lure is easy. Start by opening the weedguard and insert it into the rear of your tube bait. Continue till the tube is all the way through, making a straight presentation. Finish by resetting the weedguard on the point of the hook, never over the barb. Comes in Blonde Red finish. 4.3 UltraPoint® Technology Opti-Angle Needle Point Ringed eye Nor-Tempered Blonde red finish</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>MHK1012</v>
+      </c>
+      <c r="B129">
+        <v>112</v>
+      </c>
+      <c r="C129" t="str">
+        <v>Ultra Lock™ Soft Plastics Hook</v>
+      </c>
+      <c r="D129" t="str">
+        <v/>
+      </c>
+      <c r="E129" t="str">
+        <v/>
+      </c>
+      <c r="F129" t="str">
+        <v/>
+      </c>
+      <c r="G129" t="str">
+        <v>曲柄钩 / Offset / Wide Gap</v>
+      </c>
+      <c r="H129" t="str">
+        <v>pkgGear/images/hook/MUSTAD/ultra_lock_soft_plastics_hook.jpg</v>
+      </c>
+      <c r="I129" t="str">
+        <v/>
+      </c>
+      <c r="J129" t="str">
+        <v/>
+      </c>
+      <c r="K129" t="str">
+        <v>The Mustad Ultra Lock™ hooks feature Z-Bend offset hook that securely anchors a wide range of baits. It is an ideal choice for a wide range of large soft plastic lures such as shads, worms or swim baits. This hook is perfect for fishing around heavy cover targeting a wide variety of species, such as Bass, Perch, Brown Trout, Rainbow Trout, Zander, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point Ringed eye Forged Nor-Tempered</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>MHK1013</v>
+      </c>
+      <c r="B130">
+        <v>112</v>
+      </c>
+      <c r="C130" t="str">
+        <v>Grip-Pin Max® Flippin’ &amp; Worm Hook - 2X Strong</v>
+      </c>
+      <c r="D130" t="str">
+        <v/>
+      </c>
+      <c r="E130" t="str">
+        <v/>
+      </c>
+      <c r="F130" t="str">
+        <v/>
+      </c>
+      <c r="G130" t="str">
+        <v>倒钓钩 / Drop Shot</v>
+      </c>
+      <c r="H130" t="str">
+        <v>pkgGear/images/hook/MUSTAD/grip_pin_max_flippin_worm_hook_2x_strong.jpg</v>
+      </c>
+      <c r="I130" t="str">
+        <v/>
+      </c>
+      <c r="J130" t="str">
+        <v/>
+      </c>
+      <c r="K130" t="str">
+        <v>The Grip-Pin Max hook is designed for soft plastic worms or swim baits. It features a coated PVC pin that securely anchors the front end of soft plastic lure with a "no slip, no slide" design. It is a perfect setup for fishing a weedless hook point for that really big fish. This strong hook makes a great platform for fishing near hard cover and vegetation, using a whole range of plastic softbaits. Fish it weightless or as a Texas or Drop Shot rig. The 2X strong hook, features a straight shank and wide bend for the best hooking and holding capacity. Use it for Bass, Perch, Brown Trout, Rainbow Trout, Zander, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point Straight shank 2X Strong Extra wide bend Ringed Eye Nor-Tempered Resin-coated Grip Pin Max™ Black Nickel finish</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>MHK1014</v>
+      </c>
+      <c r="B131">
+        <v>112</v>
+      </c>
+      <c r="C131" t="str">
+        <v>Impact™ Soft Plastics Hook with Weedguard</v>
+      </c>
+      <c r="D131" t="str">
+        <v/>
+      </c>
+      <c r="E131" t="str">
+        <v/>
+      </c>
+      <c r="F131" t="str">
+        <v/>
+      </c>
+      <c r="G131" t="str">
+        <v>特种钩 / Bass Hook</v>
+      </c>
+      <c r="H131" t="str">
+        <v>pkgGear/images/hook/MUSTAD/impact_soft_plastics_hook_with_weedguard.jpg</v>
+      </c>
+      <c r="I131" t="str">
+        <v/>
+      </c>
+      <c r="J131" t="str">
+        <v/>
+      </c>
+      <c r="K131" t="str">
+        <v>Fishing around heavy cover, roots or vegetation can prove a challenge without a weedless hook. The Mustad Impact™ Soft Plastic hook has a thin wire weedguard that prevents the hook from snagging. Perfect for tube bait soft lures. Rigging the tube lure is easy. Start by opening the weedguard and insert it into the rear of your tube bait. Continue till the tube is all the way through, making a straight presentation. Finish by resetting the weedguard on the point of the hook, never over the barb. Use it for Bass, Perch, Zander, Pike or Walleye. The hook features a build-in rear weight for perfect balancing. Black nickel finish. Weight: 1/32oz/0.9g. 4.3 UltraPoint® Technology Opti-Angle Needle Point Ringed eye Weedguard Nor-Tempered Built-in 1/32oz/0.9g weight Black Nickel finish</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>MHK1015</v>
+      </c>
+      <c r="B132">
+        <v>112</v>
+      </c>
+      <c r="C132" t="str">
+        <v>KVD Grip-Pin® Hook - 2X Fine</v>
+      </c>
+      <c r="D132" t="str">
+        <v/>
+      </c>
+      <c r="E132" t="str">
+        <v/>
+      </c>
+      <c r="F132" t="str">
+        <v/>
+      </c>
+      <c r="G132" t="str">
+        <v>曲柄钩 / Offset / Wide Gap</v>
+      </c>
+      <c r="H132" t="str">
+        <v>pkgGear/images/hook/MUSTAD/kvd_grip_pin_hook_2x_fine.jpg</v>
+      </c>
+      <c r="I132" t="str">
+        <v/>
+      </c>
+      <c r="J132" t="str">
+        <v/>
+      </c>
+      <c r="K132" t="str">
+        <v>The Kevin VanDam Soft Plastic hooks feature a molded resin pin that securely anchors a wide range of baits to the hook for a "no slip, no slide" design without tearing the soft bait. The extra wide bend hook is ideal choice for a wide range of soft plastic lures such as shads, worms or swim baits. It is a great choice for lightweight Texas rigs finesse presentation using thin line. Use it to catch Bass, Perch, Brown Trout, Rainbow Trout, Zander, Pike or Walleye. Coated with Mustad's own Black Nickel finish, which is 4 times as rust resistant as traditional Black Nickel. 4.3 UltraPoint® Technology Opti-Angle Needle Point Extra wide bend 2X Fine Wire Resin-coated Grip Pin® Ringed eye Forged Nor-Tempered Black Nickel finish</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>MHK1016</v>
+      </c>
+      <c r="B133">
+        <v>112</v>
+      </c>
+      <c r="C133" t="str">
+        <v>Assault Wide Gap Hook</v>
+      </c>
+      <c r="D133" t="str">
+        <v/>
+      </c>
+      <c r="E133" t="str">
+        <v/>
+      </c>
+      <c r="F133" t="str">
+        <v/>
+      </c>
+      <c r="G133" t="str">
+        <v>曲柄钩 / Offset / Wide Gap</v>
+      </c>
+      <c r="H133" t="str">
+        <v>pkgGear/images/hook/MUSTAD/assault_wide_gap_hook.png</v>
+      </c>
+      <c r="I133" t="str">
+        <v/>
+      </c>
+      <c r="J133" t="str">
+        <v/>
+      </c>
+      <c r="K133" t="str">
+        <v>Mustad Assault Wide Gap Hook are built for landing lunkers. For versatile applications, these bass hooks are made for high hook-up ratios and secured hook-sets on big fish. The Z-bend and epoxy at the eye holds and protects soft plastics, perfect for wide gap hook applications like Texas and Carolina rigs, while also great when flipping. Mustad’s new Tak-bend places the point above the eye and at a more level angle with the bait, making the lure flush with the point and improving hook-sets compared to traditional bends. The aggressive bend gets plastic out of the way on a bite for quick penetration while also preserving strength and integrity when fish try to throw the hook. With Mustad’s AlphaPoint® hook point technology, precision fishing takes advantage of the slimmer, ridiculously sharp point combined with the durability anglers expect from Mustad. The nano-thin TitanX finish with a sleek gun-metal look supports the sharpness of the hook and the smoothness maximizes penetration. 4.8 AlphaPoint® Technology Opti-Angle Needle Point 1X Strong Z-Bend Ringed eye Forged Nor-Tempered</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>MHK1017</v>
+      </c>
+      <c r="B134">
+        <v>112</v>
+      </c>
+      <c r="C134" t="str">
+        <v>Ultra Lock™ Soft Plastics Hook - 1X Fine</v>
+      </c>
+      <c r="D134" t="str">
+        <v/>
+      </c>
+      <c r="E134" t="str">
+        <v/>
+      </c>
+      <c r="F134" t="str">
+        <v/>
+      </c>
+      <c r="G134" t="str">
+        <v>曲柄钩 / Offset / Wide Gap</v>
+      </c>
+      <c r="H134" t="str">
+        <v>pkgGear/images/hook/MUSTAD/ultra_lock_soft_plastics_hook_1x_fine.jpg</v>
+      </c>
+      <c r="I134" t="str">
+        <v/>
+      </c>
+      <c r="J134" t="str">
+        <v/>
+      </c>
+      <c r="K134" t="str">
+        <v>The Mustad Ultra Lock™ Softbait Hook is perfect for delicate presentation of soft plastic worms. It is suitable for free water fishing with the hook exposed or weedless. The wide gap and offset shank provides excellent hooking and holding abilities. Fish it Texas or Carolina Rig style or just un-weighted. Use it for Bass, Perch, Zander, Pike or Walleye. Coated with Mustad's own Black Nickel finish, which is 4 times as rust resistant as traditional Black Nickel. 4.3 UltraPoint® Technology Opti-Angle Needle Point Extra wide bend Offset shank 1X Fine Wire Ringed eye Nor-Tempered</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>MHK1018</v>
+      </c>
+      <c r="B135">
+        <v>112</v>
+      </c>
+      <c r="C135" t="str">
+        <v>Offset Shank Worm Hook</v>
+      </c>
+      <c r="D135" t="str">
+        <v/>
+      </c>
+      <c r="E135" t="str">
+        <v/>
+      </c>
+      <c r="F135" t="str">
+        <v/>
+      </c>
+      <c r="G135" t="str">
+        <v>曲柄钩 / Offset / Wide Gap</v>
+      </c>
+      <c r="H135" t="str">
+        <v>pkgGear/images/hook/MUSTAD/offset_shank_worm_hook.jpg</v>
+      </c>
+      <c r="I135" t="str">
+        <v/>
+      </c>
+      <c r="J135" t="str">
+        <v/>
+      </c>
+      <c r="K135" t="str">
+        <v>The 1X fine wire Mustad Offset Worm Hook is designed for a wide range of soft plastic worms. Fish it Texas or Carolina Rig style or just free swimming. The hook features a round bend and a 90-degree Z-lock shoulder to hold baits firmly in place. Use it for Bass, Perch, Zander, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point 1X Fine Wire Ringed eye Nor-Tempered Black Nickel finish</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>MHK1019</v>
+      </c>
+      <c r="B136">
+        <v>112</v>
+      </c>
+      <c r="C136" t="str">
+        <v>Assault Heavy Hook</v>
+      </c>
+      <c r="D136" t="str">
+        <v/>
+      </c>
+      <c r="E136" t="str">
+        <v/>
+      </c>
+      <c r="F136" t="str">
+        <v/>
+      </c>
+      <c r="G136" t="str">
+        <v>曲柄钩 / Offset / Wide Gap</v>
+      </c>
+      <c r="H136" t="str">
+        <v>pkgGear/images/hook/MUSTAD/assault_heavy_hook.png</v>
+      </c>
+      <c r="I136" t="str">
+        <v/>
+      </c>
+      <c r="J136" t="str">
+        <v/>
+      </c>
+      <c r="K136" t="str">
+        <v>Fishing for big bass, monster pike, or any heavy predator among the grass calls for a tough hook built for weedless presentations. Featuring the latest precision hook point technology, the Assault Heavy hook is made for quick, solid hook-sets. Mustad's Assault Heavy hook offset the eye and point to allow perfect rigging with soft plastics with ease while holding the bait flush to the point for the ultimate weedless hook. These fish hooks offer the perfect bend for wide gap hook applications like Carolina rigs and Texas rigs as well as flipping thanks to the Z-bend and agressive AlphaPoint® red epoxy, which are designed to hold and protect lures. The combination of the aggressive bend and Mustad’s AlphaPoint® hook point technology culminates for a slimmer, sharper hook that penetrates quickly and efficiently. Using the same Opti-Angle sharpening technique as UltraPoint®, Mustad's latest hook point offers the durability Mustad known for. The nano-thin TitanX finish with a sleek gun-metal look supports the sharpness of the hook and the smoothness maximizes penetration. 4.8 AlphaPoint® Technology Opti-Angle Needle Point 2X Strong Z-Bend Ringed eye Forged Nor-Tempered</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>MHK1020</v>
+      </c>
+      <c r="B137">
+        <v>112</v>
+      </c>
+      <c r="C137" t="str">
+        <v>Alpha-Grip Finesse Hook</v>
+      </c>
+      <c r="D137" t="str">
+        <v/>
+      </c>
+      <c r="E137" t="str">
+        <v/>
+      </c>
+      <c r="F137" t="str">
+        <v/>
+      </c>
+      <c r="G137" t="str">
+        <v>曲柄钩 / Offset / Wide Gap</v>
+      </c>
+      <c r="H137" t="str">
+        <v>pkgGear/images/hook/MUSTAD/alpha_grip_finesse_hook.jpg</v>
+      </c>
+      <c r="I137" t="str">
+        <v/>
+      </c>
+      <c r="J137" t="str">
+        <v/>
+      </c>
+      <c r="K137" t="str">
+        <v>The all-new Alpha-Grip baitholder pin holds soft plastics in place in the most secure way possible. The special angle and red epoxy in the eye ensures a solid hold when fishing in the weeds. For a dependable hook-up, the Finesse hook has a carefully crafted wide gap that resists being thrown by a thrashing Bass. With Mustad’s AlphaPoint® hook point technology, precision fishing takes advantage of the slimmer, ridiculously sharp point combined with the durability anglers expect from Mustad. The nano-thin TitanX finish with a sleek gun-metal look supports the sharpness of the hook and the smoothness maximizes penetration. 4.8 AlphaPoint® Technology Opti-Angle Needle Point 1X Fine Alpha-Grip Ringed eye Forged Nor-Tempered</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>MHK1021</v>
+      </c>
+      <c r="B138">
+        <v>112</v>
+      </c>
+      <c r="C138" t="str">
+        <v>Weedless TitanX Wacky / Neko / Dropshot Hook</v>
+      </c>
+      <c r="D138" t="str">
+        <v/>
+      </c>
+      <c r="E138" t="str">
+        <v/>
+      </c>
+      <c r="F138" t="str">
+        <v/>
+      </c>
+      <c r="G138" t="str">
+        <v>倒钓钩 / Wacky</v>
+      </c>
+      <c r="H138" t="str">
+        <v>pkgGear/images/hook/MUSTAD/weedless_titanx_wacky_neko_dropshot_hook.png</v>
+      </c>
+      <c r="I138" t="str">
+        <v/>
+      </c>
+      <c r="J138" t="str">
+        <v/>
+      </c>
+      <c r="K138" t="str">
+        <v>In collaboration between Bass Tournament Pro's Jacob Powroznik and 24-times Bassmaster winner Kevin VanDam, Mustad introduces the TitanX Wacky / Neko Dropshot hook. The Mustad Weedless Wacky Hook comes with fluorocarbon weedguard attached giving the freedom for snag free fishing around structures and heavy weed. Designed with an extra-wide gap, which provides secure hookset. Rigging for wacky style is easy. Thread the hook point through the middle of your soft plastic worm so that both ends dangle on either side of the hook. If you want to reduce tearing many anglers use a rubber “O”-ring around the soft worm and secure the hook in that. The wacky style creates a lot of action to your bait, attraction the biggest Bass around. 4.3 UltraPoint® Technology Opti-Angle Needle Point Ringed eye Weedless Nor-Tempered TitanX finish</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>MHK1022</v>
+      </c>
+      <c r="B139">
+        <v>112</v>
+      </c>
+      <c r="C139" t="str">
+        <v>Impact™ Spring Keeper Hook</v>
+      </c>
+      <c r="D139" t="str">
+        <v/>
+      </c>
+      <c r="E139" t="str">
+        <v/>
+      </c>
+      <c r="F139" t="str">
+        <v/>
+      </c>
+      <c r="G139" t="str">
+        <v>曲柄钩 / Offset / Wide Gap</v>
+      </c>
+      <c r="H139" t="str">
+        <v>pkgGear/images/hook/MUSTAD/impact_spring_keeper_hook.jpg</v>
+      </c>
+      <c r="I139" t="str">
+        <v/>
+      </c>
+      <c r="J139" t="str">
+        <v/>
+      </c>
+      <c r="K139" t="str">
+        <v>The Impact™ Spring Keeper Hook is designed for Texas Rigging soft plastic swim baits, Paddel Tails or life-like fish imitations. It features a molded resin pin that securely anchors the front end of the soft plastic lure with a "no slip, no slide" design without tearing the soft bait. It is ideal for fishing weedless with perfect presentation and hooking properties. The in-line hook eye provides perfect presentation, making your lure track straight in the water. It is a perfect setup for free water fishing with the hook exposed. Fish it weightless or with a sinker in front to get at the deeper swimming fish. Use it for Bass, Perch, Brown Trout, Rainbow Trout, Zander, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point Wide Gap Ringed eye Spring keeper Nor-Tempered</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>MHK1023</v>
+      </c>
+      <c r="B140">
+        <v>112</v>
+      </c>
+      <c r="C140" t="str">
+        <v>Impact™ Straight Keeper Hook</v>
+      </c>
+      <c r="D140" t="str">
+        <v/>
+      </c>
+      <c r="E140" t="str">
+        <v/>
+      </c>
+      <c r="F140" t="str">
+        <v/>
+      </c>
+      <c r="G140" t="str">
+        <v>曲柄钩 / Offset / Wide Gap</v>
+      </c>
+      <c r="H140" t="str">
+        <v>pkgGear/images/hook/MUSTAD/impact_straight_keeper_hook.jpg</v>
+      </c>
+      <c r="I140" t="str">
+        <v/>
+      </c>
+      <c r="J140" t="str">
+        <v/>
+      </c>
+      <c r="K140" t="str">
+        <v>The Impact™ Straight Keeper Hook feature a unique ridged gripper pin, offering a secure hold for your favorite soft plastic bait. Perfect for free water fishing with the hook exposed. The wide gap provides excellent hooking and holding abilities. Fish it weedless Texas or Carolina Rig style or just un-weighted. Use it for Bass, Perch, Zander, Pike or Walleye. Coated with Mustad's own Black Nickel finish, which is 4 times as rust resistant as traditional Black Nickel. 4.3 UltraPoint® Technology Opti-Angle Needle Point Wide Gap Ridged gripper pin Ringed eye Nor-Tempered Black Nickel finish</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>MHK1024</v>
+      </c>
+      <c r="B141">
+        <v>112</v>
+      </c>
+      <c r="C141" t="str">
+        <v>Infiltrator Swim Hook</v>
+      </c>
+      <c r="D141" t="str">
+        <v/>
+      </c>
+      <c r="E141" t="str">
+        <v/>
+      </c>
+      <c r="F141" t="str">
+        <v/>
+      </c>
+      <c r="G141" t="str">
+        <v>特种钩 / Bass Hook</v>
+      </c>
+      <c r="H141" t="str">
+        <v>pkgGear/images/hook/MUSTAD/infiltrator_swim_hook.png</v>
+      </c>
+      <c r="I141" t="str">
+        <v/>
+      </c>
+      <c r="J141" t="str">
+        <v/>
+      </c>
+      <c r="K141" t="str">
+        <v>A new, aggressive shape sets the stage for a strong update to the Mustad soft plastics hook range. The sharp angle at the bend of the hook situates the lure flush with the point, for the ultimate weedless bait. With a strong spring rigged at the inline eye, the Inflitrator Swim Hook holds baits in place, bite after bite. With Mustad’s AlphaPoint® hook point technology, precision fishing takes advantage of the slimmer, ridiculously sharp point combined with the durability anglers expect from Mustad. The nano-thin TitanX finish with a sleek gun-metal look supports the sharpness of the hook and the smoothness maximizes penetration. 4.8 AlphaPoint® Technology Opti-Angle Needle Point 2X Strong Ringed eye Forged Nor-Tempered Features Alpha Spring™ keeper</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K116"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K141"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/GearSage-client/rate/excel/hook.xlsx
+++ b/GearSage-client/rate/excel/hook.xlsx
@@ -4619,7 +4619,7 @@
         <v/>
       </c>
       <c r="G121" t="str">
-        <v>曲柄钩 / Offset / Wide Gap</v>
+        <v>倒钓钩 / Drop Shot</v>
       </c>
       <c r="H121" t="str">
         <v>pkgGear/images/hook/MUSTAD/double_wide_gap_dropshot_hook.png</v>

--- a/GearSage-client/rate/excel/hook.xlsx
+++ b/GearSage-client/rate/excel/hook.xlsx
@@ -32,7 +32,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
+  <numFmts count="5">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
   </numFmts>
   <fonts count="1">
@@ -457,7 +461,7 @@
         <v>特种钩 / Antenna / Gika</v>
       </c>
       <c r="H2" t="str">
-        <v>pkgGear/images/hook/GAMAKATSU/antenna_hook.webp</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/antenna_hook.webp</v>
       </c>
       <c r="I2" t="str">
         <v/>
@@ -492,7 +496,7 @@
         <v>倒钓钩 / Drop Shot</v>
       </c>
       <c r="H3" t="str">
-        <v>pkgGear/images/hook/GAMAKATSU/super_tuned_drop_shot.webp</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/super_tuned_drop_shot.webp</v>
       </c>
       <c r="I3" t="str">
         <v/>
@@ -527,7 +531,7 @@
         <v>圆钩 / Weedless Circle</v>
       </c>
       <c r="H4" t="str">
-        <v>pkgGear/images/hook/GAMAKATSU/catfish_circle_weedless.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/catfish_circle_weedless.jpg</v>
       </c>
       <c r="I4" t="str">
         <v/>
@@ -562,7 +566,7 @@
         <v>特种钩 / Stiletto</v>
       </c>
       <c r="H5" t="str">
-        <v>pkgGear/images/hook/GAMAKATSU/stiletto.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/stiletto.jpg</v>
       </c>
       <c r="I5" t="str">
         <v/>
@@ -597,7 +601,7 @@
         <v>直柄钩 / Aberdeen</v>
       </c>
       <c r="H6" t="str">
-        <v>pkgGear/images/hook/GAMAKATSU/sticker.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/sticker.jpg</v>
       </c>
       <c r="I6" t="str">
         <v/>
@@ -632,7 +636,7 @@
         <v>直柄钩 / Trout Stinger</v>
       </c>
       <c r="H7" t="str">
-        <v>pkgGear/images/hook/GAMAKATSU/trout_stinger.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/trout_stinger.jpg</v>
       </c>
       <c r="I7" t="str">
         <v/>
@@ -667,7 +671,7 @@
         <v>挂钩 / Spin Bait</v>
       </c>
       <c r="H8" t="str">
-        <v>pkgGear/images/hook/GAMAKATSU/spin_bait.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/spin_bait.jpg</v>
       </c>
       <c r="I8" t="str">
         <v/>
@@ -702,7 +706,7 @@
         <v>直柄钩 / Aberdeen</v>
       </c>
       <c r="H9" t="str">
-        <v>pkgGear/images/hook/GAMAKATSU/aberdeen.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/aberdeen.jpg</v>
       </c>
       <c r="I9" t="str">
         <v/>
@@ -737,7 +741,7 @@
         <v>倒钓钩 / Wacky Weedless</v>
       </c>
       <c r="H10" t="str">
-        <v>pkgGear/images/hook/GAMAKATSU/wicked_wacky.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/wicked_wacky.jpg</v>
       </c>
       <c r="I10" t="str">
         <v/>
@@ -772,7 +776,7 @@
         <v>曲柄钩 / Wide Gap</v>
       </c>
       <c r="H11" t="str">
-        <v>pkgGear/images/hook/GAMAKATSU/walleye_wide_gap.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/walleye_wide_gap.jpg</v>
       </c>
       <c r="I11" t="str">
         <v/>
@@ -807,7 +811,7 @@
         <v>直柄钩 / Trout Worm</v>
       </c>
       <c r="H12" t="str">
-        <v>pkgGear/images/hook/GAMAKATSU/tw_hook.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/tw_hook.jpg</v>
       </c>
       <c r="I12" t="str">
         <v/>
@@ -842,7 +846,7 @@
         <v>挂钩 / Trailer Hook</v>
       </c>
       <c r="H13" t="str">
-        <v>pkgGear/images/hook/GAMAKATSU/trailer_hook_sp.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/trailer_hook_sp.jpg</v>
       </c>
       <c r="I13" t="str">
         <v/>
@@ -877,7 +881,7 @@
         <v>倒钓钩 / Drop Shot Weedless</v>
       </c>
       <c r="H14" t="str">
-        <v>pkgGear/images/hook/GAMAKATSU/split_shot_drop_shot_weedless.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/split_shot_drop_shot_weedless.jpg</v>
       </c>
       <c r="I14" t="str">
         <v/>
@@ -912,7 +916,7 @@
         <v>倒钓钩 / Drop Shot</v>
       </c>
       <c r="H15" t="str">
-        <v>pkgGear/images/hook/GAMAKATSU/split_shot_drop_shot.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/split_shot_drop_shot.jpg</v>
       </c>
       <c r="I15" t="str">
         <v/>
@@ -947,7 +951,7 @@
         <v>挂钩 / Spinnerbait Trailer</v>
       </c>
       <c r="H16" t="str">
-        <v>pkgGear/images/hook/GAMAKATSU/spinner_bait.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/spinner_bait.jpg</v>
       </c>
       <c r="I16" t="str">
         <v/>
@@ -982,7 +986,7 @@
         <v>直柄钩 / Egg Hook / Barb on Shank</v>
       </c>
       <c r="H17" t="str">
-        <v>pkgGear/images/hook/GAMAKATSU/single_egg_hook_barb_on_shank.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/single_egg_hook_barb_on_shank.jpg</v>
       </c>
       <c r="I17" t="str">
         <v/>
@@ -1017,7 +1021,7 @@
         <v>直柄钩 / Upturned Eye</v>
       </c>
       <c r="H18" t="str">
-        <v>pkgGear/images/hook/GAMAKATSU/shiner_upturned_eye.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/shiner_upturned_eye.jpg</v>
       </c>
       <c r="I18" t="str">
         <v/>
@@ -1052,7 +1056,7 @@
         <v>直柄钩 / Straight Eye</v>
       </c>
       <c r="H19" t="str">
-        <v>pkgGear/images/hook/GAMAKATSU/shiner_straight_eye.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/shiner_straight_eye.jpg</v>
       </c>
       <c r="I19" t="str">
         <v/>
@@ -1087,7 +1091,7 @@
         <v>曲柄钩 / Micro Wide Gap</v>
       </c>
       <c r="H20" t="str">
-        <v>pkgGear/images/hook/GAMAKATSU/micro_wide_gap.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/micro_wide_gap.jpg</v>
       </c>
       <c r="I20" t="str">
         <v/>
@@ -1122,7 +1126,7 @@
         <v>曲柄钩 / Micro V Gap</v>
       </c>
       <c r="H21" t="str">
-        <v>pkgGear/images/hook/GAMAKATSU/micro_v_gap.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/micro_v_gap.jpg</v>
       </c>
       <c r="I21" t="str">
         <v/>
@@ -1157,7 +1161,7 @@
         <v>曲柄钩 / Micro Perfect Gap</v>
       </c>
       <c r="H22" t="str">
-        <v>pkgGear/images/hook/GAMAKATSU/micro_perfect_gap.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/micro_perfect_gap.jpg</v>
       </c>
       <c r="I22" t="str">
         <v/>
@@ -1192,7 +1196,7 @@
         <v>挂钩 / Stinger</v>
       </c>
       <c r="H23" t="str">
-        <v>pkgGear/images/hook/GAMAKATSU/g_stinger.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/g_stinger.jpg</v>
       </c>
       <c r="I23" t="str">
         <v/>
@@ -1227,7 +1231,7 @@
         <v>鲤鱼钩 / Super Hook</v>
       </c>
       <c r="H24" t="str">
-        <v>pkgGear/images/hook/GAMAKATSU/g_carp_super_hook.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/g_carp_super_hook.jpg</v>
       </c>
       <c r="I24" t="str">
         <v/>
@@ -1262,7 +1266,7 @@
         <v>鲤鱼钩 / Specialist RX</v>
       </c>
       <c r="H25" t="str">
-        <v>pkgGear/images/hook/GAMAKATSU/g_carp_specialist_rx.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/g_carp_specialist_rx.jpg</v>
       </c>
       <c r="I25" t="str">
         <v/>
@@ -1297,7 +1301,7 @@
         <v>鲤鱼钩 / Specialist R</v>
       </c>
       <c r="H26" t="str">
-        <v>pkgGear/images/hook/GAMAKATSU/g_carp_specialist_r.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/g_carp_specialist_r.jpg</v>
       </c>
       <c r="I26" t="str">
         <v/>
@@ -1332,7 +1336,7 @@
         <v>鲤鱼钩 / Hump Back</v>
       </c>
       <c r="H27" t="str">
-        <v>pkgGear/images/hook/GAMAKATSU/g_carp_hump_back.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/g_carp_hump_back.jpg</v>
       </c>
       <c r="I27" t="str">
         <v/>
@@ -1367,7 +1371,7 @@
         <v>曲柄钩 / Finesse Wide Gap Weedless</v>
       </c>
       <c r="H28" t="str">
-        <v>pkgGear/images/hook/GAMAKATSU/finesse_wide_gap_weedless.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/finesse_wide_gap_weedless.jpg</v>
       </c>
       <c r="I28" t="str">
         <v/>
@@ -1402,7 +1406,7 @@
         <v>曲柄钩 / Finesse Wide Gap</v>
       </c>
       <c r="H29" t="str">
-        <v>pkgGear/images/hook/GAMAKATSU/finesse_wide_gap.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/finesse_wide_gap.jpg</v>
       </c>
       <c r="I29" t="str">
         <v/>
@@ -1437,7 +1441,7 @@
         <v>组合钩 / Assortment</v>
       </c>
       <c r="H30" t="str">
-        <v>pkgGear/images/hook/GAMAKATSU/crappie_assortment.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/crappie_assortment.jpg</v>
       </c>
       <c r="I30" t="str">
         <v/>
@@ -1472,7 +1476,7 @@
         <v>组合钩 / Assortment</v>
       </c>
       <c r="H31" t="str">
-        <v>pkgGear/images/hook/GAMAKATSU/catfish_assortment.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/catfish_assortment.jpg</v>
       </c>
       <c r="I31" t="str">
         <v/>
@@ -1507,7 +1511,7 @@
         <v>圆钩 / Big Cat Circle</v>
       </c>
       <c r="H32" t="str">
-        <v>pkgGear/images/hook/GAMAKATSU/big_cat_circle.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/big_cat_circle.jpg</v>
       </c>
       <c r="I32" t="str">
         <v/>
@@ -1542,7 +1546,7 @@
         <v>倒钓钩 / Drop Shot</v>
       </c>
       <c r="H33" t="str">
-        <v>pkgGear/images/hook/OWNER/jungle_drop_shot.gif</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/jungle_drop_shot.gif</v>
       </c>
       <c r="I33" t="str">
         <v/>
@@ -1577,7 +1581,7 @@
         <v>曲柄钩 / Offset / Wide Gap</v>
       </c>
       <c r="H34" t="str">
-        <v>pkgGear/images/hook/OWNER/multi_offset.gif</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/multi_offset.gif</v>
       </c>
       <c r="I34" t="str">
         <v/>
@@ -1612,7 +1616,7 @@
         <v>特种钩 / Bass Hook</v>
       </c>
       <c r="H35" t="str">
-        <v>pkgGear/images/hook/OWNER/ringed_all_purpose_softbait_hook.gif</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/ringed_all_purpose_softbait_hook.gif</v>
       </c>
       <c r="I35" t="str">
         <v/>
@@ -1647,7 +1651,7 @@
         <v>曲柄钩 / Offset / Wide Gap</v>
       </c>
       <c r="H36" t="str">
-        <v>pkgGear/images/hook/OWNER/haymaker.gif</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/haymaker.gif</v>
       </c>
       <c r="I36" t="str">
         <v/>
@@ -1682,7 +1686,7 @@
         <v>曲柄钩 / Offset / Wide Gap</v>
       </c>
       <c r="H37" t="str">
-        <v>pkgGear/images/hook/OWNER/offset_shank_wide_gap_red.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/offset_shank_wide_gap_red.jpg</v>
       </c>
       <c r="I37" t="str">
         <v/>
@@ -1717,7 +1721,7 @@
         <v>特种钩 / Swimbait</v>
       </c>
       <c r="H38" t="str">
-        <v>pkgGear/images/hook/OWNER/flashy_swimmer_silver_colorado.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/flashy_swimmer_silver_colorado.jpg</v>
       </c>
       <c r="I38" t="str">
         <v/>
@@ -1752,7 +1756,7 @@
         <v>特种钩 / Swimbait</v>
       </c>
       <c r="H39" t="str">
-        <v>pkgGear/images/hook/OWNER/flashy_swimmer_gold_willowleaf.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/flashy_swimmer_gold_willowleaf.jpg</v>
       </c>
       <c r="I39" t="str">
         <v/>
@@ -1787,7 +1791,7 @@
         <v>特种钩 / Bass Hook</v>
       </c>
       <c r="H40" t="str">
-        <v>pkgGear/images/hook/OWNER/jungle_flipping_hd.gif</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/jungle_flipping_hd.gif</v>
       </c>
       <c r="I40" t="str">
         <v/>
@@ -1822,7 +1826,7 @@
         <v>倒钓钩 / Drop Shot</v>
       </c>
       <c r="H41" t="str">
-        <v>pkgGear/images/hook/OWNER/cover_shot_hd.gif</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/cover_shot_hd.gif</v>
       </c>
       <c r="I41" t="str">
         <v/>
@@ -1857,7 +1861,7 @@
         <v>曲柄钩 / Offset / Wide Gap</v>
       </c>
       <c r="H42" t="str">
-        <v>pkgGear/images/hook/OWNER/sniper_finesse.gif</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/sniper_finesse.gif</v>
       </c>
       <c r="I42" t="str">
         <v/>
@@ -1892,7 +1896,7 @@
         <v>倒钓钩 / Wacky</v>
       </c>
       <c r="H43" t="str">
-        <v>pkgGear/images/hook/OWNER/jungle_wacky.gif</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/jungle_wacky.gif</v>
       </c>
       <c r="I43" t="str">
         <v/>
@@ -1927,7 +1931,7 @@
         <v>特种钩 / Swimbait</v>
       </c>
       <c r="H44" t="str">
-        <v>pkgGear/images/hook/OWNER/flashy_swimmer_gold_colorado.gif</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/flashy_swimmer_gold_colorado.gif</v>
       </c>
       <c r="I44" t="str">
         <v/>
@@ -1962,7 +1966,7 @@
         <v>曲柄钩 / Offset / Wide Gap</v>
       </c>
       <c r="H45" t="str">
-        <v>pkgGear/images/hook/OWNER/jungle_wide_gap.gif</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/jungle_wide_gap.gif</v>
       </c>
       <c r="I45" t="str">
         <v/>
@@ -1997,7 +2001,7 @@
         <v>倒钓钩 / Drop Shot</v>
       </c>
       <c r="H46" t="str">
-        <v>pkgGear/images/hook/OWNER/cover_shot.gif</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/cover_shot.gif</v>
       </c>
       <c r="I46" t="str">
         <v/>
@@ -2032,7 +2036,7 @@
         <v>曲柄钩 / Offset / Wide Gap</v>
       </c>
       <c r="H47" t="str">
-        <v>pkgGear/images/hook/OWNER/offset_shank_wide_gap.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/offset_shank_wide_gap.jpg</v>
       </c>
       <c r="I47" t="str">
         <v/>
@@ -2067,7 +2071,7 @@
         <v>特种钩 / Bass Hook</v>
       </c>
       <c r="H48" t="str">
-        <v>pkgGear/images/hook/OWNER/toad_hook.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/toad_hook.jpg</v>
       </c>
       <c r="I48" t="str">
         <v/>
@@ -2102,7 +2106,7 @@
         <v>曲柄钩 / Offset / Wide Gap</v>
       </c>
       <c r="H49" t="str">
-        <v>pkgGear/images/hook/OWNER/wide_gap_plus.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/wide_gap_plus.jpg</v>
       </c>
       <c r="I49" t="str">
         <v/>
@@ -2137,7 +2141,7 @@
         <v>特种钩 / Bass Hook</v>
       </c>
       <c r="H50" t="str">
-        <v>pkgGear/images/hook/OWNER/stinger_harness_rig.gif</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/stinger_harness_rig.gif</v>
       </c>
       <c r="I50" t="str">
         <v/>
@@ -2172,7 +2176,7 @@
         <v>特种钩 / Bass Hook</v>
       </c>
       <c r="H51" t="str">
-        <v>pkgGear/images/hook/OWNER/twistlock_light_weighted.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/twistlock_light_weighted.jpg</v>
       </c>
       <c r="I51" t="str">
         <v/>
@@ -2207,7 +2211,7 @@
         <v>曲柄钩 / Offset / Wide Gap</v>
       </c>
       <c r="H52" t="str">
-        <v>pkgGear/images/hook/OWNER/j_light.gif</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/j_light.gif</v>
       </c>
       <c r="I52" t="str">
         <v/>
@@ -2242,7 +2246,7 @@
         <v>特种钩 / Bass Hook</v>
       </c>
       <c r="H53" t="str">
-        <v>pkgGear/images/hook/OWNER/rig_n_hook.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/rig_n_hook.jpg</v>
       </c>
       <c r="I53" t="str">
         <v/>
@@ -2277,7 +2281,7 @@
         <v>倒钓钩 / Wacky</v>
       </c>
       <c r="H54" t="str">
-        <v>pkgGear/images/hook/OWNER/wacky_hook.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/wacky_hook.jpg</v>
       </c>
       <c r="I54" t="str">
         <v/>
@@ -2312,7 +2316,7 @@
         <v>特种钩 / Bass Hook</v>
       </c>
       <c r="H55" t="str">
-        <v>pkgGear/images/hook/OWNER/twistlock_3x_weighted.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/twistlock_3x_weighted.jpg</v>
       </c>
       <c r="I55" t="str">
         <v/>
@@ -2347,7 +2351,7 @@
         <v>特种钩 / Bass Hook</v>
       </c>
       <c r="H56" t="str">
-        <v>pkgGear/images/hook/OWNER/twistlock_3x.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/twistlock_3x.jpg</v>
       </c>
       <c r="I56" t="str">
         <v/>
@@ -2382,7 +2386,7 @@
         <v>特种钩 / Swimbait</v>
       </c>
       <c r="H57" t="str">
-        <v>pkgGear/images/hook/OWNER/beast_weighted.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/beast_weighted.jpg</v>
       </c>
       <c r="I57" t="str">
         <v/>
@@ -2417,7 +2421,7 @@
         <v>特种钩 / Swimbait</v>
       </c>
       <c r="H58" t="str">
-        <v>pkgGear/images/hook/OWNER/beast_hook.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/beast_hook.jpg</v>
       </c>
       <c r="I58" t="str">
         <v/>
@@ -2452,7 +2456,7 @@
         <v>特种钩 / Swimbait</v>
       </c>
       <c r="H59" t="str">
-        <v>pkgGear/images/hook/OWNER/flashy_swimmer_beast_version.gif</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/flashy_swimmer_beast_version.gif</v>
       </c>
       <c r="I59" t="str">
         <v/>
@@ -2487,7 +2491,7 @@
         <v>特种钩 / Bass Hook</v>
       </c>
       <c r="H60" t="str">
-        <v>pkgGear/images/hook/OWNER/twistlock_light.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/twistlock_light.jpg</v>
       </c>
       <c r="I60" t="str">
         <v/>
@@ -2522,7 +2526,7 @@
         <v>特种钩 / Bass Hook</v>
       </c>
       <c r="H61" t="str">
-        <v>pkgGear/images/hook/OWNER/twistlock_flipping_hook.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/twistlock_flipping_hook.jpg</v>
       </c>
       <c r="I61" t="str">
         <v/>
@@ -2557,7 +2561,7 @@
         <v>曲柄钩 / Offset / Wide Gap</v>
       </c>
       <c r="H62" t="str">
-        <v>pkgGear/images/hook/OWNER/all_purpose_softbait_hook.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/all_purpose_softbait_hook.jpg</v>
       </c>
       <c r="I62" t="str">
         <v/>
@@ -2592,7 +2596,7 @@
         <v>曲柄钩 / Offset / Wide Gap</v>
       </c>
       <c r="H63" t="str">
-        <v>pkgGear/images/hook/OWNER/all_purpose_worm_hook.gif</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/all_purpose_worm_hook.gif</v>
       </c>
       <c r="I63" t="str">
         <v/>
@@ -2627,7 +2631,7 @@
         <v>特种钩 / Bass Hook</v>
       </c>
       <c r="H64" t="str">
-        <v>pkgGear/images/hook/OWNER/jungle_flipping_hook.gif</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/jungle_flipping_hook.gif</v>
       </c>
       <c r="I64" t="str">
         <v/>
@@ -2662,7 +2666,7 @@
         <v>曲柄钩 / Offset / Wide Gap</v>
       </c>
       <c r="H65" t="str">
-        <v>pkgGear/images/hook/OWNER/oversize_worm_hook.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/oversize_worm_hook.jpg</v>
       </c>
       <c r="I65" t="str">
         <v/>
@@ -2697,7 +2701,7 @@
         <v>曲柄钩 / Offset / Wide Gap</v>
       </c>
       <c r="H66" t="str">
-        <v>pkgGear/images/hook/OWNER/j_hook.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/j_hook.jpg</v>
       </c>
       <c r="I66" t="str">
         <v/>
@@ -2732,7 +2736,7 @@
         <v>曲柄钩 / Offset / Wide Gap</v>
       </c>
       <c r="H67" t="str">
-        <v>pkgGear/images/hook/OWNER/straight_shank_wide_gap.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/straight_shank_wide_gap.jpg</v>
       </c>
       <c r="I67" t="str">
         <v/>
@@ -2767,7 +2771,7 @@
         <v>曲柄钩 / Offset / Wide Gap</v>
       </c>
       <c r="H68" t="str">
-        <v>pkgGear/images/hook/OWNER/straight_shank.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/straight_shank.jpg</v>
       </c>
       <c r="I68" t="str">
         <v/>
@@ -2802,7 +2806,7 @@
         <v>特种钩 / Bass Hook</v>
       </c>
       <c r="H69" t="str">
-        <v>pkgGear/images/hook/OWNER/phantom_tube_hook.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/phantom_tube_hook.jpg</v>
       </c>
       <c r="I69" t="str">
         <v/>
@@ -2837,7 +2841,7 @@
         <v>特种钩 / Bass Hook</v>
       </c>
       <c r="H70" t="str">
-        <v>pkgGear/images/hook/OWNER/mosquito_hook.gif</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/mosquito_hook.gif</v>
       </c>
       <c r="I70" t="str">
         <v/>
@@ -2872,7 +2876,7 @@
         <v>曲柄钩 / Offset / Wide Gap</v>
       </c>
       <c r="H71" t="str">
-        <v>pkgGear/images/hook/OWNER/offset_shank.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/offset_shank.jpg</v>
       </c>
       <c r="I71" t="str">
         <v/>
@@ -2907,7 +2911,7 @@
         <v>特种钩 / Swimbait</v>
       </c>
       <c r="H72" t="str">
-        <v>pkgGear/images/hook/OWNER/flashy_swimmer_silver_willowleaf.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/flashy_swimmer_silver_willowleaf.jpg</v>
       </c>
       <c r="I72" t="str">
         <v/>
@@ -4482,7 +4486,7 @@
         <v>曲柄钩 / Offset / Wide Gap</v>
       </c>
       <c r="H117" t="str">
-        <v>pkgGear/images/hook/MUSTAD/grip_pin_big_bite_soft_plastics_hook.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/grip_pin_big_bite_soft_plastics_hook.jpg</v>
       </c>
       <c r="I117" t="str">
         <v/>
@@ -4517,7 +4521,7 @@
         <v>倒钓钩 / Drop Shot</v>
       </c>
       <c r="H118" t="str">
-        <v>pkgGear/images/hook/MUSTAD/select_finesse_hook_1x_fine.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/select_finesse_hook_1x_fine.jpg</v>
       </c>
       <c r="I118" t="str">
         <v/>
@@ -4552,7 +4556,7 @@
         <v>曲柄钩 / Offset / Wide Gap</v>
       </c>
       <c r="H119" t="str">
-        <v>pkgGear/images/hook/MUSTAD/kvd_grip_pin_soft_plastics_hook.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/kvd_grip_pin_soft_plastics_hook.jpg</v>
       </c>
       <c r="I119" t="str">
         <v/>
@@ -4587,7 +4591,7 @@
         <v>倒钓钩 / Drop Shot</v>
       </c>
       <c r="H120" t="str">
-        <v>pkgGear/images/hook/MUSTAD/grip_pin_edge_finesse_soft_plastics_hook.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/grip_pin_edge_finesse_soft_plastics_hook.jpg</v>
       </c>
       <c r="I120" t="str">
         <v/>
@@ -4622,7 +4626,7 @@
         <v>倒钓钩 / Drop Shot</v>
       </c>
       <c r="H121" t="str">
-        <v>pkgGear/images/hook/MUSTAD/double_wide_gap_dropshot_hook.png</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/double_wide_gap_dropshot_hook.png</v>
       </c>
       <c r="I121" t="str">
         <v/>
@@ -4657,7 +4661,7 @@
         <v>倒钓钩 / Drop Shot</v>
       </c>
       <c r="H122" t="str">
-        <v>pkgGear/images/hook/MUSTAD/dropshot_hook.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/dropshot_hook.jpg</v>
       </c>
       <c r="I122" t="str">
         <v/>
@@ -4692,7 +4696,7 @@
         <v>倒钓钩 / Drop Shot</v>
       </c>
       <c r="H123" t="str">
-        <v>pkgGear/images/hook/MUSTAD/titanx_wacky_neko_dropshot_hook.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/titanx_wacky_neko_dropshot_hook.jpg</v>
       </c>
       <c r="I123" t="str">
         <v/>
@@ -4727,7 +4731,7 @@
         <v>曲柄钩 / Offset / Wide Gap</v>
       </c>
       <c r="H124" t="str">
-        <v>pkgGear/images/hook/MUSTAD/mega_bite_soft_plastics_hook.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/mega_bite_soft_plastics_hook.jpg</v>
       </c>
       <c r="I124" t="str">
         <v/>
@@ -4762,7 +4766,7 @@
         <v>曲柄钩 / Offset / Wide Gap</v>
       </c>
       <c r="H125" t="str">
-        <v>pkgGear/images/hook/MUSTAD/big_mouth_tube_hook.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/big_mouth_tube_hook.jpg</v>
       </c>
       <c r="I125" t="str">
         <v/>
@@ -4797,7 +4801,7 @@
         <v>曲柄钩 / Offset / Wide Gap</v>
       </c>
       <c r="H126" t="str">
-        <v>pkgGear/images/hook/MUSTAD/weighted_kvd_grip_pin_hook.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/weighted_kvd_grip_pin_hook.jpg</v>
       </c>
       <c r="I126" t="str">
         <v/>
@@ -4832,7 +4836,7 @@
         <v>特种钩 / Swimbait Hook</v>
       </c>
       <c r="H127" t="str">
-        <v>pkgGear/images/hook/MUSTAD/power_lock_plus_spring_keeper_hook_weighted.png</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/power_lock_plus_spring_keeper_hook_weighted.png</v>
       </c>
       <c r="I127" t="str">
         <v/>
@@ -4867,7 +4871,7 @@
         <v>倒钓钩 / Wacky</v>
       </c>
       <c r="H128" t="str">
-        <v>pkgGear/images/hook/MUSTAD/kvd_weedless_wacky_worm_hook.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/kvd_weedless_wacky_worm_hook.jpg</v>
       </c>
       <c r="I128" t="str">
         <v/>
@@ -4902,7 +4906,7 @@
         <v>曲柄钩 / Offset / Wide Gap</v>
       </c>
       <c r="H129" t="str">
-        <v>pkgGear/images/hook/MUSTAD/ultra_lock_soft_plastics_hook.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/ultra_lock_soft_plastics_hook.jpg</v>
       </c>
       <c r="I129" t="str">
         <v/>
@@ -4937,7 +4941,7 @@
         <v>倒钓钩 / Drop Shot</v>
       </c>
       <c r="H130" t="str">
-        <v>pkgGear/images/hook/MUSTAD/grip_pin_max_flippin_worm_hook_2x_strong.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/grip_pin_max_flippin_worm_hook_2x_strong.jpg</v>
       </c>
       <c r="I130" t="str">
         <v/>
@@ -4972,7 +4976,7 @@
         <v>特种钩 / Bass Hook</v>
       </c>
       <c r="H131" t="str">
-        <v>pkgGear/images/hook/MUSTAD/impact_soft_plastics_hook_with_weedguard.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/impact_soft_plastics_hook_with_weedguard.jpg</v>
       </c>
       <c r="I131" t="str">
         <v/>
@@ -5007,7 +5011,7 @@
         <v>曲柄钩 / Offset / Wide Gap</v>
       </c>
       <c r="H132" t="str">
-        <v>pkgGear/images/hook/MUSTAD/kvd_grip_pin_hook_2x_fine.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/kvd_grip_pin_hook_2x_fine.jpg</v>
       </c>
       <c r="I132" t="str">
         <v/>
@@ -5042,7 +5046,7 @@
         <v>曲柄钩 / Offset / Wide Gap</v>
       </c>
       <c r="H133" t="str">
-        <v>pkgGear/images/hook/MUSTAD/assault_wide_gap_hook.png</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/assault_wide_gap_hook.png</v>
       </c>
       <c r="I133" t="str">
         <v/>
@@ -5077,7 +5081,7 @@
         <v>曲柄钩 / Offset / Wide Gap</v>
       </c>
       <c r="H134" t="str">
-        <v>pkgGear/images/hook/MUSTAD/ultra_lock_soft_plastics_hook_1x_fine.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/ultra_lock_soft_plastics_hook_1x_fine.jpg</v>
       </c>
       <c r="I134" t="str">
         <v/>
@@ -5112,7 +5116,7 @@
         <v>曲柄钩 / Offset / Wide Gap</v>
       </c>
       <c r="H135" t="str">
-        <v>pkgGear/images/hook/MUSTAD/offset_shank_worm_hook.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/offset_shank_worm_hook.jpg</v>
       </c>
       <c r="I135" t="str">
         <v/>
@@ -5147,7 +5151,7 @@
         <v>曲柄钩 / Offset / Wide Gap</v>
       </c>
       <c r="H136" t="str">
-        <v>pkgGear/images/hook/MUSTAD/assault_heavy_hook.png</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/assault_heavy_hook.png</v>
       </c>
       <c r="I136" t="str">
         <v/>
@@ -5182,7 +5186,7 @@
         <v>曲柄钩 / Offset / Wide Gap</v>
       </c>
       <c r="H137" t="str">
-        <v>pkgGear/images/hook/MUSTAD/alpha_grip_finesse_hook.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/alpha_grip_finesse_hook.jpg</v>
       </c>
       <c r="I137" t="str">
         <v/>
@@ -5217,7 +5221,7 @@
         <v>倒钓钩 / Wacky</v>
       </c>
       <c r="H138" t="str">
-        <v>pkgGear/images/hook/MUSTAD/weedless_titanx_wacky_neko_dropshot_hook.png</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/weedless_titanx_wacky_neko_dropshot_hook.png</v>
       </c>
       <c r="I138" t="str">
         <v/>
@@ -5252,7 +5256,7 @@
         <v>曲柄钩 / Offset / Wide Gap</v>
       </c>
       <c r="H139" t="str">
-        <v>pkgGear/images/hook/MUSTAD/impact_spring_keeper_hook.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/impact_spring_keeper_hook.jpg</v>
       </c>
       <c r="I139" t="str">
         <v/>
@@ -5287,7 +5291,7 @@
         <v>曲柄钩 / Offset / Wide Gap</v>
       </c>
       <c r="H140" t="str">
-        <v>pkgGear/images/hook/MUSTAD/impact_straight_keeper_hook.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/impact_straight_keeper_hook.jpg</v>
       </c>
       <c r="I140" t="str">
         <v/>
@@ -5322,7 +5326,7 @@
         <v>特种钩 / Bass Hook</v>
       </c>
       <c r="H141" t="str">
-        <v>pkgGear/images/hook/MUSTAD/infiltrator_swim_hook.png</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/infiltrator_swim_hook.png</v>
       </c>
       <c r="I141" t="str">
         <v/>

--- a/GearSage-client/rate/excel/hook.xlsx
+++ b/GearSage-client/rate/excel/hook.xlsx
@@ -458,7 +458,7 @@
         <v/>
       </c>
       <c r="G2" t="str">
-        <v>特种钩 / Antenna / Gika</v>
+        <v>特种钩</v>
       </c>
       <c r="H2" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/antenna_hook.webp</v>
@@ -493,7 +493,7 @@
         <v/>
       </c>
       <c r="G3" t="str">
-        <v>倒钓钩 / Drop Shot</v>
+        <v>倒钓钩</v>
       </c>
       <c r="H3" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/super_tuned_drop_shot.webp</v>
@@ -528,7 +528,7 @@
         <v/>
       </c>
       <c r="G4" t="str">
-        <v>圆钩 / Weedless Circle</v>
+        <v>圆钩</v>
       </c>
       <c r="H4" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/catfish_circle_weedless.jpg</v>
@@ -563,7 +563,7 @@
         <v/>
       </c>
       <c r="G5" t="str">
-        <v>特种钩 / Stiletto</v>
+        <v>直柄钩</v>
       </c>
       <c r="H5" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/stiletto.jpg</v>
@@ -598,7 +598,7 @@
         <v/>
       </c>
       <c r="G6" t="str">
-        <v>直柄钩 / Aberdeen</v>
+        <v>直柄钩</v>
       </c>
       <c r="H6" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/sticker.jpg</v>
@@ -633,7 +633,7 @@
         <v/>
       </c>
       <c r="G7" t="str">
-        <v>直柄钩 / Trout Stinger</v>
+        <v>直柄钩</v>
       </c>
       <c r="H7" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/trout_stinger.jpg</v>
@@ -668,7 +668,7 @@
         <v/>
       </c>
       <c r="G8" t="str">
-        <v>挂钩 / Spin Bait</v>
+        <v>辅助挂钩</v>
       </c>
       <c r="H8" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/spin_bait.jpg</v>
@@ -703,7 +703,7 @@
         <v/>
       </c>
       <c r="G9" t="str">
-        <v>直柄钩 / Aberdeen</v>
+        <v>直柄钩</v>
       </c>
       <c r="H9" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/aberdeen.jpg</v>
@@ -738,7 +738,7 @@
         <v/>
       </c>
       <c r="G10" t="str">
-        <v>倒钓钩 / Wacky Weedless</v>
+        <v>Wacky/Neko钩</v>
       </c>
       <c r="H10" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/wicked_wacky.jpg</v>
@@ -773,7 +773,7 @@
         <v/>
       </c>
       <c r="G11" t="str">
-        <v>曲柄钩 / Wide Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H11" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/walleye_wide_gap.jpg</v>
@@ -808,7 +808,7 @@
         <v/>
       </c>
       <c r="G12" t="str">
-        <v>直柄钩 / Trout Worm</v>
+        <v>直柄钩</v>
       </c>
       <c r="H12" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/tw_hook.jpg</v>
@@ -843,7 +843,7 @@
         <v/>
       </c>
       <c r="G13" t="str">
-        <v>挂钩 / Trailer Hook</v>
+        <v>辅助挂钩</v>
       </c>
       <c r="H13" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/trailer_hook_sp.jpg</v>
@@ -878,7 +878,7 @@
         <v/>
       </c>
       <c r="G14" t="str">
-        <v>倒钓钩 / Drop Shot Weedless</v>
+        <v>倒钓钩</v>
       </c>
       <c r="H14" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/split_shot_drop_shot_weedless.jpg</v>
@@ -913,7 +913,7 @@
         <v/>
       </c>
       <c r="G15" t="str">
-        <v>倒钓钩 / Drop Shot</v>
+        <v>倒钓钩</v>
       </c>
       <c r="H15" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/split_shot_drop_shot.jpg</v>
@@ -948,7 +948,7 @@
         <v/>
       </c>
       <c r="G16" t="str">
-        <v>挂钩 / Spinnerbait Trailer</v>
+        <v>辅助挂钩</v>
       </c>
       <c r="H16" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/spinner_bait.jpg</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="G17" t="str">
-        <v>直柄钩 / Egg Hook / Barb on Shank</v>
+        <v>直柄钩</v>
       </c>
       <c r="H17" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/single_egg_hook_barb_on_shank.jpg</v>
@@ -1018,7 +1018,7 @@
         <v/>
       </c>
       <c r="G18" t="str">
-        <v>直柄钩 / Upturned Eye</v>
+        <v>直柄钩</v>
       </c>
       <c r="H18" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/shiner_upturned_eye.jpg</v>
@@ -1053,7 +1053,7 @@
         <v/>
       </c>
       <c r="G19" t="str">
-        <v>直柄钩 / Straight Eye</v>
+        <v>直柄钩</v>
       </c>
       <c r="H19" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/shiner_straight_eye.jpg</v>
@@ -1088,7 +1088,7 @@
         <v/>
       </c>
       <c r="G20" t="str">
-        <v>曲柄钩 / Micro Wide Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H20" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/micro_wide_gap.jpg</v>
@@ -1123,7 +1123,7 @@
         <v/>
       </c>
       <c r="G21" t="str">
-        <v>曲柄钩 / Micro V Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H21" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/micro_v_gap.jpg</v>
@@ -1158,7 +1158,7 @@
         <v/>
       </c>
       <c r="G22" t="str">
-        <v>曲柄钩 / Micro Perfect Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H22" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/micro_perfect_gap.jpg</v>
@@ -1193,7 +1193,7 @@
         <v/>
       </c>
       <c r="G23" t="str">
-        <v>挂钩 / Stinger</v>
+        <v>辅助挂钩</v>
       </c>
       <c r="H23" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/g_stinger.jpg</v>
@@ -1228,7 +1228,7 @@
         <v/>
       </c>
       <c r="G24" t="str">
-        <v>鲤鱼钩 / Super Hook</v>
+        <v>鲤鱼钩</v>
       </c>
       <c r="H24" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/g_carp_super_hook.jpg</v>
@@ -1263,7 +1263,7 @@
         <v/>
       </c>
       <c r="G25" t="str">
-        <v>鲤鱼钩 / Specialist RX</v>
+        <v>鲤鱼钩</v>
       </c>
       <c r="H25" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/g_carp_specialist_rx.jpg</v>
@@ -1298,7 +1298,7 @@
         <v/>
       </c>
       <c r="G26" t="str">
-        <v>鲤鱼钩 / Specialist R</v>
+        <v>鲤鱼钩</v>
       </c>
       <c r="H26" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/g_carp_specialist_r.jpg</v>
@@ -1333,7 +1333,7 @@
         <v/>
       </c>
       <c r="G27" t="str">
-        <v>鲤鱼钩 / Hump Back</v>
+        <v>鲤鱼钩</v>
       </c>
       <c r="H27" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/g_carp_hump_back.jpg</v>
@@ -1368,7 +1368,7 @@
         <v/>
       </c>
       <c r="G28" t="str">
-        <v>曲柄钩 / Finesse Wide Gap Weedless</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H28" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/finesse_wide_gap_weedless.jpg</v>
@@ -1403,7 +1403,7 @@
         <v/>
       </c>
       <c r="G29" t="str">
-        <v>曲柄钩 / Finesse Wide Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H29" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/finesse_wide_gap.jpg</v>
@@ -1438,7 +1438,7 @@
         <v/>
       </c>
       <c r="G30" t="str">
-        <v>组合钩 / Assortment</v>
+        <v>组合装</v>
       </c>
       <c r="H30" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/crappie_assortment.jpg</v>
@@ -1473,7 +1473,7 @@
         <v/>
       </c>
       <c r="G31" t="str">
-        <v>组合钩 / Assortment</v>
+        <v>组合装</v>
       </c>
       <c r="H31" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/catfish_assortment.jpg</v>
@@ -1508,7 +1508,7 @@
         <v/>
       </c>
       <c r="G32" t="str">
-        <v>圆钩 / Big Cat Circle</v>
+        <v>圆钩</v>
       </c>
       <c r="H32" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/big_cat_circle.jpg</v>
@@ -1543,7 +1543,7 @@
         <v/>
       </c>
       <c r="G33" t="str">
-        <v>倒钓钩 / Drop Shot</v>
+        <v>倒钓钩</v>
       </c>
       <c r="H33" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/jungle_drop_shot.gif</v>
@@ -1578,7 +1578,7 @@
         <v/>
       </c>
       <c r="G34" t="str">
-        <v>曲柄钩 / Offset / Wide Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H34" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/multi_offset.gif</v>
@@ -1613,7 +1613,7 @@
         <v/>
       </c>
       <c r="G35" t="str">
-        <v>特种钩 / Bass Hook</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H35" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/ringed_all_purpose_softbait_hook.gif</v>
@@ -1648,7 +1648,7 @@
         <v/>
       </c>
       <c r="G36" t="str">
-        <v>曲柄钩 / Offset / Wide Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H36" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/haymaker.gif</v>
@@ -1683,7 +1683,7 @@
         <v/>
       </c>
       <c r="G37" t="str">
-        <v>曲柄钩 / Offset / Wide Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H37" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/offset_shank_wide_gap_red.jpg</v>
@@ -1718,7 +1718,7 @@
         <v/>
       </c>
       <c r="G38" t="str">
-        <v>特种钩 / Swimbait</v>
+        <v>Swimbait钩</v>
       </c>
       <c r="H38" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/flashy_swimmer_silver_colorado.jpg</v>
@@ -1753,7 +1753,7 @@
         <v/>
       </c>
       <c r="G39" t="str">
-        <v>特种钩 / Swimbait</v>
+        <v>Swimbait钩</v>
       </c>
       <c r="H39" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/flashy_swimmer_gold_willowleaf.jpg</v>
@@ -1788,7 +1788,7 @@
         <v/>
       </c>
       <c r="G40" t="str">
-        <v>特种钩 / Bass Hook</v>
+        <v>直柄钩</v>
       </c>
       <c r="H40" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/jungle_flipping_hd.gif</v>
@@ -1823,7 +1823,7 @@
         <v/>
       </c>
       <c r="G41" t="str">
-        <v>倒钓钩 / Drop Shot</v>
+        <v>倒钓钩</v>
       </c>
       <c r="H41" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/cover_shot_hd.gif</v>
@@ -1858,7 +1858,7 @@
         <v/>
       </c>
       <c r="G42" t="str">
-        <v>曲柄钩 / Offset / Wide Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H42" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/sniper_finesse.gif</v>
@@ -1893,7 +1893,7 @@
         <v/>
       </c>
       <c r="G43" t="str">
-        <v>倒钓钩 / Wacky</v>
+        <v>Wacky/Neko钩</v>
       </c>
       <c r="H43" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/jungle_wacky.gif</v>
@@ -1928,7 +1928,7 @@
         <v/>
       </c>
       <c r="G44" t="str">
-        <v>特种钩 / Swimbait</v>
+        <v>Swimbait钩</v>
       </c>
       <c r="H44" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/flashy_swimmer_gold_colorado.gif</v>
@@ -1963,7 +1963,7 @@
         <v/>
       </c>
       <c r="G45" t="str">
-        <v>曲柄钩 / Offset / Wide Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H45" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/jungle_wide_gap.gif</v>
@@ -1998,7 +1998,7 @@
         <v/>
       </c>
       <c r="G46" t="str">
-        <v>倒钓钩 / Drop Shot</v>
+        <v>倒钓钩</v>
       </c>
       <c r="H46" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/cover_shot.gif</v>
@@ -2033,7 +2033,7 @@
         <v/>
       </c>
       <c r="G47" t="str">
-        <v>曲柄钩 / Offset / Wide Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H47" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/offset_shank_wide_gap.jpg</v>
@@ -2068,7 +2068,7 @@
         <v/>
       </c>
       <c r="G48" t="str">
-        <v>特种钩 / Bass Hook</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H48" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/toad_hook.jpg</v>
@@ -2103,7 +2103,7 @@
         <v/>
       </c>
       <c r="G49" t="str">
-        <v>曲柄钩 / Offset / Wide Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H49" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/wide_gap_plus.jpg</v>
@@ -2138,7 +2138,7 @@
         <v/>
       </c>
       <c r="G50" t="str">
-        <v>特种钩 / Bass Hook</v>
+        <v>辅助挂钩</v>
       </c>
       <c r="H50" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/stinger_harness_rig.gif</v>
@@ -2173,7 +2173,7 @@
         <v/>
       </c>
       <c r="G51" t="str">
-        <v>特种钩 / Bass Hook</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H51" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/twistlock_light_weighted.jpg</v>
@@ -2208,7 +2208,7 @@
         <v/>
       </c>
       <c r="G52" t="str">
-        <v>曲柄钩 / Offset / Wide Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H52" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/j_light.gif</v>
@@ -2243,7 +2243,7 @@
         <v/>
       </c>
       <c r="G53" t="str">
-        <v>特种钩 / Bass Hook</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H53" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/rig_n_hook.jpg</v>
@@ -2278,7 +2278,7 @@
         <v/>
       </c>
       <c r="G54" t="str">
-        <v>倒钓钩 / Wacky</v>
+        <v>Wacky/Neko钩</v>
       </c>
       <c r="H54" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/wacky_hook.jpg</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="G55" t="str">
-        <v>特种钩 / Bass Hook</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H55" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/twistlock_3x_weighted.jpg</v>
@@ -2348,7 +2348,7 @@
         <v/>
       </c>
       <c r="G56" t="str">
-        <v>特种钩 / Bass Hook</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H56" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/twistlock_3x.jpg</v>
@@ -2383,7 +2383,7 @@
         <v/>
       </c>
       <c r="G57" t="str">
-        <v>特种钩 / Swimbait</v>
+        <v>Swimbait钩</v>
       </c>
       <c r="H57" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/beast_weighted.jpg</v>
@@ -2418,7 +2418,7 @@
         <v/>
       </c>
       <c r="G58" t="str">
-        <v>特种钩 / Swimbait</v>
+        <v>Swimbait钩</v>
       </c>
       <c r="H58" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/beast_hook.jpg</v>
@@ -2453,7 +2453,7 @@
         <v/>
       </c>
       <c r="G59" t="str">
-        <v>特种钩 / Swimbait</v>
+        <v>Swimbait钩</v>
       </c>
       <c r="H59" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/flashy_swimmer_beast_version.gif</v>
@@ -2488,7 +2488,7 @@
         <v/>
       </c>
       <c r="G60" t="str">
-        <v>特种钩 / Bass Hook</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H60" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/twistlock_light.jpg</v>
@@ -2523,7 +2523,7 @@
         <v/>
       </c>
       <c r="G61" t="str">
-        <v>特种钩 / Bass Hook</v>
+        <v>直柄钩</v>
       </c>
       <c r="H61" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/twistlock_flipping_hook.jpg</v>
@@ -2558,7 +2558,7 @@
         <v/>
       </c>
       <c r="G62" t="str">
-        <v>曲柄钩 / Offset / Wide Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H62" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/all_purpose_softbait_hook.jpg</v>
@@ -2593,7 +2593,7 @@
         <v/>
       </c>
       <c r="G63" t="str">
-        <v>曲柄钩 / Offset / Wide Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H63" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/all_purpose_worm_hook.gif</v>
@@ -2628,7 +2628,7 @@
         <v/>
       </c>
       <c r="G64" t="str">
-        <v>特种钩 / Bass Hook</v>
+        <v>直柄钩</v>
       </c>
       <c r="H64" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/jungle_flipping_hook.gif</v>
@@ -2663,7 +2663,7 @@
         <v/>
       </c>
       <c r="G65" t="str">
-        <v>曲柄钩 / Offset / Wide Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H65" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/oversize_worm_hook.jpg</v>
@@ -2698,7 +2698,7 @@
         <v/>
       </c>
       <c r="G66" t="str">
-        <v>曲柄钩 / Offset / Wide Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H66" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/j_hook.jpg</v>
@@ -2733,7 +2733,7 @@
         <v/>
       </c>
       <c r="G67" t="str">
-        <v>曲柄钩 / Offset / Wide Gap</v>
+        <v>直柄钩</v>
       </c>
       <c r="H67" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/straight_shank_wide_gap.jpg</v>
@@ -2768,7 +2768,7 @@
         <v/>
       </c>
       <c r="G68" t="str">
-        <v>曲柄钩 / Offset / Wide Gap</v>
+        <v>直柄钩</v>
       </c>
       <c r="H68" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/straight_shank.jpg</v>
@@ -2803,7 +2803,7 @@
         <v/>
       </c>
       <c r="G69" t="str">
-        <v>特种钩 / Bass Hook</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H69" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/phantom_tube_hook.jpg</v>
@@ -2838,7 +2838,7 @@
         <v/>
       </c>
       <c r="G70" t="str">
-        <v>特种钩 / Bass Hook</v>
+        <v>倒钓钩</v>
       </c>
       <c r="H70" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/mosquito_hook.gif</v>
@@ -2873,7 +2873,7 @@
         <v/>
       </c>
       <c r="G71" t="str">
-        <v>曲柄钩 / Offset / Wide Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H71" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/offset_shank.jpg</v>
@@ -2908,7 +2908,7 @@
         <v/>
       </c>
       <c r="G72" t="str">
-        <v>特种钩 / Swimbait</v>
+        <v>Swimbait钩</v>
       </c>
       <c r="H72" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/OWNER_hooks/flashy_swimmer_silver_willowleaf.jpg</v>
@@ -4483,7 +4483,7 @@
         <v/>
       </c>
       <c r="G117" t="str">
-        <v>曲柄钩 / Offset / Wide Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H117" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/grip_pin_big_bite_soft_plastics_hook.jpg</v>
@@ -4518,7 +4518,7 @@
         <v/>
       </c>
       <c r="G118" t="str">
-        <v>倒钓钩 / Drop Shot</v>
+        <v>倒钓钩</v>
       </c>
       <c r="H118" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/select_finesse_hook_1x_fine.jpg</v>
@@ -4553,7 +4553,7 @@
         <v/>
       </c>
       <c r="G119" t="str">
-        <v>曲柄钩 / Offset / Wide Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H119" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/kvd_grip_pin_soft_plastics_hook.jpg</v>
@@ -4588,7 +4588,7 @@
         <v/>
       </c>
       <c r="G120" t="str">
-        <v>倒钓钩 / Drop Shot</v>
+        <v>直柄钩</v>
       </c>
       <c r="H120" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/grip_pin_edge_finesse_soft_plastics_hook.jpg</v>
@@ -4623,7 +4623,7 @@
         <v/>
       </c>
       <c r="G121" t="str">
-        <v>倒钓钩 / Drop Shot</v>
+        <v>倒钓钩</v>
       </c>
       <c r="H121" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/double_wide_gap_dropshot_hook.png</v>
@@ -4658,7 +4658,7 @@
         <v/>
       </c>
       <c r="G122" t="str">
-        <v>倒钓钩 / Drop Shot</v>
+        <v>倒钓钩</v>
       </c>
       <c r="H122" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/dropshot_hook.jpg</v>
@@ -4693,7 +4693,7 @@
         <v/>
       </c>
       <c r="G123" t="str">
-        <v>倒钓钩 / Drop Shot</v>
+        <v>Wacky/Neko钩</v>
       </c>
       <c r="H123" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/titanx_wacky_neko_dropshot_hook.jpg</v>
@@ -4728,7 +4728,7 @@
         <v/>
       </c>
       <c r="G124" t="str">
-        <v>曲柄钩 / Offset / Wide Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H124" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/mega_bite_soft_plastics_hook.jpg</v>
@@ -4763,7 +4763,7 @@
         <v/>
       </c>
       <c r="G125" t="str">
-        <v>曲柄钩 / Offset / Wide Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H125" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/big_mouth_tube_hook.jpg</v>
@@ -4798,7 +4798,7 @@
         <v/>
       </c>
       <c r="G126" t="str">
-        <v>曲柄钩 / Offset / Wide Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H126" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/weighted_kvd_grip_pin_hook.jpg</v>
@@ -4833,7 +4833,7 @@
         <v/>
       </c>
       <c r="G127" t="str">
-        <v>特种钩 / Swimbait Hook</v>
+        <v>Swimbait钩</v>
       </c>
       <c r="H127" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/power_lock_plus_spring_keeper_hook_weighted.png</v>
@@ -4868,7 +4868,7 @@
         <v/>
       </c>
       <c r="G128" t="str">
-        <v>倒钓钩 / Wacky</v>
+        <v>Wacky/Neko钩</v>
       </c>
       <c r="H128" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/kvd_weedless_wacky_worm_hook.jpg</v>
@@ -4903,7 +4903,7 @@
         <v/>
       </c>
       <c r="G129" t="str">
-        <v>曲柄钩 / Offset / Wide Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H129" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/ultra_lock_soft_plastics_hook.jpg</v>
@@ -4938,7 +4938,7 @@
         <v/>
       </c>
       <c r="G130" t="str">
-        <v>倒钓钩 / Drop Shot</v>
+        <v>直柄钩</v>
       </c>
       <c r="H130" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/grip_pin_max_flippin_worm_hook_2x_strong.jpg</v>
@@ -4973,7 +4973,7 @@
         <v/>
       </c>
       <c r="G131" t="str">
-        <v>特种钩 / Bass Hook</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H131" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/impact_soft_plastics_hook_with_weedguard.jpg</v>
@@ -5008,7 +5008,7 @@
         <v/>
       </c>
       <c r="G132" t="str">
-        <v>曲柄钩 / Offset / Wide Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H132" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/kvd_grip_pin_hook_2x_fine.jpg</v>
@@ -5043,7 +5043,7 @@
         <v/>
       </c>
       <c r="G133" t="str">
-        <v>曲柄钩 / Offset / Wide Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H133" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/assault_wide_gap_hook.png</v>
@@ -5078,7 +5078,7 @@
         <v/>
       </c>
       <c r="G134" t="str">
-        <v>曲柄钩 / Offset / Wide Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H134" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/ultra_lock_soft_plastics_hook_1x_fine.jpg</v>
@@ -5113,7 +5113,7 @@
         <v/>
       </c>
       <c r="G135" t="str">
-        <v>曲柄钩 / Offset / Wide Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H135" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/offset_shank_worm_hook.jpg</v>
@@ -5148,7 +5148,7 @@
         <v/>
       </c>
       <c r="G136" t="str">
-        <v>曲柄钩 / Offset / Wide Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H136" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/assault_heavy_hook.png</v>
@@ -5183,7 +5183,7 @@
         <v/>
       </c>
       <c r="G137" t="str">
-        <v>曲柄钩 / Offset / Wide Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H137" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/alpha_grip_finesse_hook.jpg</v>
@@ -5218,7 +5218,7 @@
         <v/>
       </c>
       <c r="G138" t="str">
-        <v>倒钓钩 / Wacky</v>
+        <v>Wacky/Neko钩</v>
       </c>
       <c r="H138" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/weedless_titanx_wacky_neko_dropshot_hook.png</v>
@@ -5253,7 +5253,7 @@
         <v/>
       </c>
       <c r="G139" t="str">
-        <v>曲柄钩 / Offset / Wide Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H139" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/impact_spring_keeper_hook.jpg</v>
@@ -5288,7 +5288,7 @@
         <v/>
       </c>
       <c r="G140" t="str">
-        <v>曲柄钩 / Offset / Wide Gap</v>
+        <v>直柄钩</v>
       </c>
       <c r="H140" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/impact_straight_keeper_hook.jpg</v>
@@ -5323,7 +5323,7 @@
         <v/>
       </c>
       <c r="G141" t="str">
-        <v>特种钩 / Bass Hook</v>
+        <v>Swimbait钩</v>
       </c>
       <c r="H141" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/infiltrator_swim_hook.png</v>
